--- a/교환반품.xlsx
+++ b/교환반품.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@반품률대시보드\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C76F7F-E4C5-4747-8D47-91D7E7C7E1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D1A35B-AB46-400F-B40C-A84D64307DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{54D7FD6B-5922-43C6-B06D-5BC838DADD53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$520</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="555">
   <si>
     <t>교환</t>
   </si>
@@ -60,9 +63,6 @@
   </si>
   <si>
     <t>취소</t>
-  </si>
-  <si>
-    <t>첫 구매 당사부담</t>
   </si>
   <si>
     <t>접수일</t>
@@ -1432,43 +1432,6 @@
     <t>첫구매 당사부담</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>첫구매</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>당사부담</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 당사부담</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>202508211959528700</t>
   </si>
   <si>
@@ -1683,11 +1646,6 @@
     <t>14100148289689</t>
   </si>
   <si>
-    <t>당사부담
-(부분환불)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>O20251017210147020365-816072-001</t>
   </si>
   <si>
@@ -1868,6 +1826,9 @@
   <si>
     <t>S251229150859-0
 20251229-0001392</t>
+  </si>
+  <si>
+    <t>미청구(N배송)</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1911,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1966,12 +1927,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2011,7 +1966,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2051,9 +2006,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2066,10 +2018,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2439,16 +2388,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2459,13 +2408,13 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2473,16 +2422,16 @@
         <v>45720</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2490,16 +2439,16 @@
         <v>45720</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2507,16 +2456,16 @@
         <v>45720</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2524,16 +2473,16 @@
         <v>45720</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2541,16 +2490,16 @@
         <v>45720</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2558,16 +2507,16 @@
         <v>45720</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2575,16 +2524,16 @@
         <v>45721</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2592,16 +2541,16 @@
         <v>45721</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2612,13 +2561,13 @@
         <v>4</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2629,13 +2578,13 @@
         <v>4</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2643,16 +2592,16 @@
         <v>45723</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2660,16 +2609,16 @@
         <v>45726</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2677,16 +2626,16 @@
         <v>45726</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2694,16 +2643,16 @@
         <v>45726</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2711,16 +2660,16 @@
         <v>45726</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2728,16 +2677,16 @@
         <v>45727</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2745,16 +2694,16 @@
         <v>45727</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2762,16 +2711,16 @@
         <v>45728</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2779,16 +2728,16 @@
         <v>45728</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2796,16 +2745,16 @@
         <v>45729</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2813,16 +2762,16 @@
         <v>45729</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2830,16 +2779,16 @@
         <v>45729</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2847,16 +2796,16 @@
         <v>45729</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2864,16 +2813,16 @@
         <v>45730</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2881,16 +2830,16 @@
         <v>45730</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2898,16 +2847,16 @@
         <v>45730</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2918,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>5</v>
@@ -2932,16 +2881,16 @@
         <v>45733</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2949,16 +2898,16 @@
         <v>45733</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2966,16 +2915,16 @@
         <v>45734</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2983,16 +2932,16 @@
         <v>45734</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3000,16 +2949,16 @@
         <v>45734</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3017,13 +2966,13 @@
         <v>45741</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>1</v>
@@ -3034,10 +2983,10 @@
         <v>45741</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>5</v>
@@ -3054,7 +3003,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>5</v>
@@ -3068,13 +3017,13 @@
         <v>45741</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>1</v>
@@ -3085,13 +3034,13 @@
         <v>45742</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>1</v>
@@ -3102,13 +3051,13 @@
         <v>45742</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>0</v>
@@ -3119,13 +3068,13 @@
         <v>45743</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>0</v>
@@ -3136,13 +3085,13 @@
         <v>45743</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>0</v>
@@ -3153,10 +3102,10 @@
         <v>45743</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>5</v>
@@ -3170,13 +3119,13 @@
         <v>45744</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>0</v>
@@ -3187,13 +3136,13 @@
         <v>45744</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>0</v>
@@ -3204,10 +3153,10 @@
         <v>45744</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>5</v>
@@ -3221,13 +3170,13 @@
         <v>45744</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>1</v>
@@ -3241,7 +3190,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>5</v>
@@ -3255,10 +3204,10 @@
         <v>45747</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>5</v>
@@ -3272,13 +3221,13 @@
         <v>45747</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>1</v>
@@ -3289,13 +3238,13 @@
         <v>45747</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>0</v>
@@ -3306,13 +3255,13 @@
         <v>45747</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>0</v>
@@ -3323,13 +3272,13 @@
         <v>45747</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>0</v>
@@ -3340,13 +3289,13 @@
         <v>45659</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>0</v>
@@ -3360,7 +3309,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>5</v>
@@ -3377,7 +3326,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>5</v>
@@ -3394,10 +3343,10 @@
         <v>2</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>0</v>
@@ -3408,13 +3357,13 @@
         <v>45660</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>5</v>
+        <v>84</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>1</v>
@@ -3425,13 +3374,13 @@
         <v>45660</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>5</v>
+        <v>85</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>0</v>
@@ -3445,10 +3394,10 @@
         <v>2</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>1</v>
@@ -3459,10 +3408,10 @@
         <v>45663</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>5</v>
@@ -3476,10 +3425,10 @@
         <v>45664</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>5</v>
@@ -3493,13 +3442,13 @@
         <v>45665</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>5</v>
+        <v>89</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>1</v>
@@ -3510,13 +3459,13 @@
         <v>45665</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>1</v>
@@ -3527,10 +3476,10 @@
         <v>45666</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>5</v>
@@ -3544,10 +3493,10 @@
         <v>45666</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>5</v>
@@ -3561,13 +3510,13 @@
         <v>45667</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>5</v>
+        <v>93</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>1</v>
@@ -3578,13 +3527,13 @@
         <v>45667</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>5</v>
+        <v>94</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>1</v>
@@ -3595,13 +3544,13 @@
         <v>45667</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>5</v>
+        <v>95</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>1</v>
@@ -3612,13 +3561,13 @@
         <v>45667</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>5</v>
+        <v>96</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>0</v>
@@ -3629,13 +3578,13 @@
         <v>45667</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>0</v>
@@ -3646,13 +3595,13 @@
         <v>45670</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>5</v>
+        <v>98</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>0</v>
@@ -3663,13 +3612,13 @@
         <v>45670</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>1</v>
@@ -3680,13 +3629,13 @@
         <v>45671</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>0</v>
@@ -3697,13 +3646,13 @@
         <v>45671</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>5</v>
+        <v>101</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>1</v>
@@ -3714,10 +3663,10 @@
         <v>45673</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>5</v>
@@ -3731,10 +3680,10 @@
         <v>45677</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>5</v>
@@ -3751,7 +3700,7 @@
         <v>2</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>5</v>
@@ -3765,1009 +3714,1009 @@
         <v>45679</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>5</v>
+        <v>105</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="14">
+      <c r="A80" s="13">
         <v>45691</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" s="15" t="s">
+      <c r="B80" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="13">
+        <v>45693</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D80" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E80" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="14">
-        <v>45693</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C81" s="15" t="s">
+      <c r="D81" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="13">
+        <v>45694</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D81" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="14">
+      <c r="D82" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="13">
         <v>45694</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C82" s="15" t="s">
+      <c r="B83" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D82" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E82" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="14">
+      <c r="D83" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="13">
         <v>45694</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B84" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="13">
+        <v>45695</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="13">
+        <v>45695</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="13">
+        <v>45695</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="13">
+        <v>45695</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="13">
+        <v>45698</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E89" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="13">
+        <v>45698</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="13">
+        <v>45698</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="13">
+        <v>45698</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="13">
+        <v>45698</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="13">
+        <v>45699</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="13">
+        <v>45699</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="13">
+        <v>45699</v>
+      </c>
+      <c r="B96" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D83" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="14">
-        <v>45694</v>
-      </c>
-      <c r="B84" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="14">
-        <v>45695</v>
-      </c>
-      <c r="B85" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="14">
-        <v>45695</v>
-      </c>
-      <c r="B86" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="14">
-        <v>45695</v>
-      </c>
-      <c r="B87" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="14">
-        <v>45695</v>
-      </c>
-      <c r="B88" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E88" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="14">
-        <v>45698</v>
-      </c>
-      <c r="B89" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="14">
-        <v>45698</v>
-      </c>
-      <c r="B90" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E90" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="14">
-        <v>45698</v>
-      </c>
-      <c r="B91" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="14">
-        <v>45698</v>
-      </c>
-      <c r="B92" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E92" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="14">
-        <v>45698</v>
-      </c>
-      <c r="B93" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E93" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="14">
+      <c r="C96" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="13">
         <v>45699</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C94" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="14">
+      <c r="B97" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="13">
         <v>45699</v>
       </c>
-      <c r="B95" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C95" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="14">
-        <v>45699</v>
-      </c>
-      <c r="B96" s="15" t="s">
+      <c r="B98" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="13">
+        <v>45700</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="13">
+        <v>45700</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="13">
+        <v>45700</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="13">
+        <v>45701</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="13">
+        <v>45701</v>
+      </c>
+      <c r="B103" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C96" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="14">
-        <v>45699</v>
-      </c>
-      <c r="B97" s="15" t="s">
+      <c r="C103" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="13">
+        <v>45701</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="13">
+        <v>45701</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E105" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="13">
+        <v>45702</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E106" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="13">
+        <v>45702</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E107" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="13">
+        <v>45702</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="13">
+        <v>45702</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="13">
+        <v>45702</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E110" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="13">
+        <v>45705</v>
+      </c>
+      <c r="B111" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E111" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="13">
+        <v>45705</v>
+      </c>
+      <c r="B112" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E112" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="13">
+        <v>45706</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E113" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="13">
+        <v>45706</v>
+      </c>
+      <c r="B114" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="13">
+        <v>45706</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="13">
+        <v>45707</v>
+      </c>
+      <c r="B116" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="13">
+        <v>45707</v>
+      </c>
+      <c r="B117" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C97" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E97" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="14">
-        <v>45699</v>
-      </c>
-      <c r="B98" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C98" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E98" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="14">
-        <v>45700</v>
-      </c>
-      <c r="B99" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C99" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E99" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="14">
-        <v>45700</v>
-      </c>
-      <c r="B100" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D100" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="14">
-        <v>45700</v>
-      </c>
-      <c r="B101" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C101" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D101" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="14">
-        <v>45701</v>
-      </c>
-      <c r="B102" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C102" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D102" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="14">
-        <v>45701</v>
-      </c>
-      <c r="B103" s="15" t="s">
+      <c r="C117" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D117" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="13">
+        <v>45708</v>
+      </c>
+      <c r="B118" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C103" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D103" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="14">
-        <v>45701</v>
-      </c>
-      <c r="B104" s="15" t="s">
+      <c r="C118" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D118" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="13">
+        <v>45708</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D119" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E119" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="13">
+        <v>45708</v>
+      </c>
+      <c r="B120" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C104" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D104" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E104" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="14">
-        <v>45701</v>
-      </c>
-      <c r="B105" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D105" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E105" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="14">
-        <v>45702</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C106" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E106" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="14">
-        <v>45702</v>
-      </c>
-      <c r="B107" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E107" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="14">
-        <v>45702</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E108" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="14">
-        <v>45702</v>
-      </c>
-      <c r="B109" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C109" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D109" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E109" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="14">
-        <v>45702</v>
-      </c>
-      <c r="B110" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C110" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E110" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="14">
-        <v>45705</v>
-      </c>
-      <c r="B111" s="15" t="s">
+      <c r="C120" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E120" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="13">
+        <v>45708</v>
+      </c>
+      <c r="B121" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C111" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D111" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E111" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="14">
-        <v>45705</v>
-      </c>
-      <c r="B112" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C112" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D112" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E112" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="14">
-        <v>45706</v>
-      </c>
-      <c r="B113" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E113" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="14">
-        <v>45706</v>
-      </c>
-      <c r="B114" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C114" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E114" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="14">
-        <v>45706</v>
-      </c>
-      <c r="B115" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C115" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E115" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="14">
-        <v>45707</v>
-      </c>
-      <c r="B116" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C116" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D116" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E116" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="14">
-        <v>45707</v>
-      </c>
-      <c r="B117" s="15" t="s">
+      <c r="C121" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D121" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="13">
+        <v>45709</v>
+      </c>
+      <c r="B122" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C117" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D117" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E117" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="14">
-        <v>45708</v>
-      </c>
-      <c r="B118" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E118" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="14">
-        <v>45708</v>
-      </c>
-      <c r="B119" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C119" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E119" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="14">
-        <v>45708</v>
-      </c>
-      <c r="B120" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C120" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E120" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="14">
-        <v>45708</v>
-      </c>
-      <c r="B121" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C121" s="15" t="s">
+      <c r="C122" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D121" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E121" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="14">
-        <v>45709</v>
-      </c>
-      <c r="B122" s="15" t="s">
+      <c r="D122" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="13">
+        <v>45712</v>
+      </c>
+      <c r="B123" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="13">
+        <v>45712</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="13">
+        <v>45712</v>
+      </c>
+      <c r="B125" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E125" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="13">
+        <v>45712</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E126" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="13">
+        <v>45712</v>
+      </c>
+      <c r="B127" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C122" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E122" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="14">
+      <c r="C127" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E127" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="13">
         <v>45712</v>
       </c>
-      <c r="B123" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D123" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E123" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="14">
+      <c r="B128" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E128" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="13">
         <v>45712</v>
       </c>
-      <c r="B124" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C124" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E124" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="14">
+      <c r="B129" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D129" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="13">
         <v>45712</v>
       </c>
-      <c r="B125" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D125" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E125" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="14">
+      <c r="B130" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="13">
         <v>45712</v>
       </c>
-      <c r="B126" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C126" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D126" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E126" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="14">
-        <v>45712</v>
-      </c>
-      <c r="B127" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C127" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="D127" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E127" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="14">
-        <v>45712</v>
-      </c>
-      <c r="B128" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C128" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D128" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E128" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="14">
-        <v>45712</v>
-      </c>
-      <c r="B129" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C129" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D129" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E129" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="14">
-        <v>45712</v>
-      </c>
-      <c r="B130" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C130" s="15" t="s">
+      <c r="B131" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="D130" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E130" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="14">
-        <v>45712</v>
-      </c>
-      <c r="B131" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C131" s="15" t="s">
+      <c r="D131" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E131" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="13">
+        <v>45713</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D131" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E131" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="14">
+      <c r="D132" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="13">
         <v>45713</v>
       </c>
-      <c r="B132" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C132" s="15" t="s">
+      <c r="B133" s="14"/>
+      <c r="C133" s="14"/>
+      <c r="D133" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E133" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="13">
+        <v>45713</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C134" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D132" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E132" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="14">
-        <v>45713</v>
-      </c>
-      <c r="B133" s="15"/>
-      <c r="C133" s="15"/>
-      <c r="D133" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E133" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="14">
-        <v>45713</v>
-      </c>
-      <c r="B134" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C134" s="15" t="s">
+      <c r="D134" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E134" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="13">
+        <v>45714</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="D134" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E134" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="14">
-        <v>45714</v>
-      </c>
-      <c r="B135" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C135" s="15" t="s">
+      <c r="D135" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E135" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="13">
+        <v>45715</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="D135" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E135" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="14">
+      <c r="D136" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E136" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="13">
         <v>45715</v>
       </c>
-      <c r="B136" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C136" s="15" t="s">
+      <c r="B137" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D136" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E136" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="14">
-        <v>45715</v>
-      </c>
-      <c r="B137" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C137" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D137" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E137" s="15" t="s">
+      <c r="D137" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E137" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>5</v>
@@ -4778,16 +4727,16 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>1</v>
@@ -4795,16 +4744,16 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>1</v>
@@ -4812,16 +4761,16 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>1</v>
@@ -4829,16 +4778,16 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>0</v>
@@ -4846,16 +4795,16 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>1</v>
@@ -4863,13 +4812,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>5</v>
@@ -4880,16 +4829,16 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>0</v>
@@ -4897,16 +4846,16 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E146" s="5" t="s">
         <v>1</v>
@@ -4914,13 +4863,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>5</v>
@@ -4931,16 +4880,16 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>1</v>
@@ -4948,16 +4897,16 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>1</v>
@@ -4965,13 +4914,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>5</v>
@@ -4982,13 +4931,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>5</v>
@@ -4999,13 +4948,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>5</v>
@@ -5016,16 +4965,16 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>0</v>
@@ -5033,16 +4982,16 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D154" s="16" t="s">
-        <v>109</v>
+        <v>198</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>0</v>
@@ -5050,16 +4999,16 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D155" s="16" t="s">
-        <v>109</v>
+        <v>199</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E155" s="5" t="s">
         <v>0</v>
@@ -5067,13 +5016,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>5</v>
@@ -5084,16 +5033,16 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E157" s="5" t="s">
         <v>0</v>
@@ -5104,13 +5053,13 @@
         <v>45764</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>0</v>
@@ -5121,13 +5070,13 @@
         <v>45764</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E159" s="5" t="s">
         <v>0</v>
@@ -5138,10 +5087,10 @@
         <v>45764</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>5</v>
@@ -5155,13 +5104,13 @@
         <v>45765</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>0</v>
@@ -5172,13 +5121,13 @@
         <v>45765</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E162" s="5" t="s">
         <v>0</v>
@@ -5189,13 +5138,13 @@
         <v>45765</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E163" s="5" t="s">
         <v>0</v>
@@ -5206,13 +5155,13 @@
         <v>45765</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E164" s="5" t="s">
         <v>0</v>
@@ -5223,13 +5172,13 @@
         <v>45765</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E165" s="5" t="s">
         <v>0</v>
@@ -5240,13 +5189,13 @@
         <v>45768</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>1</v>
@@ -5257,13 +5206,13 @@
         <v>45768</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E167" s="5" t="s">
         <v>0</v>
@@ -5274,13 +5223,13 @@
         <v>45768</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>0</v>
@@ -5294,7 +5243,7 @@
         <v>4</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>5</v>
@@ -5311,7 +5260,7 @@
         <v>4</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>5</v>
@@ -5325,13 +5274,13 @@
         <v>45768</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E171" s="5" t="s">
         <v>1</v>
@@ -5342,13 +5291,13 @@
         <v>45768</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E172" s="5" t="s">
         <v>1</v>
@@ -5359,13 +5308,13 @@
         <v>45768</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>0</v>
@@ -5376,13 +5325,13 @@
         <v>45769</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E174" s="5" t="s">
         <v>0</v>
@@ -5393,13 +5342,13 @@
         <v>45770</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E175" s="5" t="s">
         <v>1</v>
@@ -5410,13 +5359,13 @@
         <v>45770</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>1</v>
@@ -5427,13 +5376,13 @@
         <v>45770</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>1</v>
@@ -5444,13 +5393,13 @@
         <v>45770</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E178" s="5" t="s">
         <v>0</v>
@@ -5464,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>5</v>
@@ -5478,13 +5427,13 @@
         <v>45771</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>0</v>
@@ -5495,13 +5444,13 @@
         <v>45771</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>0</v>
@@ -5512,10 +5461,10 @@
         <v>45772</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>5</v>
@@ -5529,13 +5478,13 @@
         <v>45772</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E183" s="5" t="s">
         <v>0</v>
@@ -5546,10 +5495,10 @@
         <v>45772</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>5</v>
@@ -5563,13 +5512,13 @@
         <v>45772</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E185" s="5" t="s">
         <v>0</v>
@@ -5580,10 +5529,10 @@
         <v>45776</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>5</v>
@@ -5597,13 +5546,13 @@
         <v>45776</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E187" s="5" t="s">
         <v>0</v>
@@ -5614,13 +5563,13 @@
         <v>45776</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E188" s="5" t="s">
         <v>1</v>
@@ -5631,13 +5580,13 @@
         <v>45776</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E189" s="5" t="s">
         <v>0</v>
@@ -5648,10 +5597,10 @@
         <v>45776</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>5</v>
@@ -5665,13 +5614,13 @@
         <v>45777</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E191" s="5" t="s">
         <v>0</v>
@@ -5682,13 +5631,13 @@
         <v>45777</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E192" s="5" t="s">
         <v>7</v>
@@ -5702,10 +5651,10 @@
         <v>4</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E193" s="5" t="s">
         <v>1</v>
@@ -5716,10 +5665,10 @@
         <v>45779</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>5</v>
@@ -5736,7 +5685,7 @@
         <v>4</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>5</v>
@@ -5750,13 +5699,13 @@
         <v>45779</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E196" s="5" t="s">
         <v>1</v>
@@ -5767,13 +5716,13 @@
         <v>45784</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E197" s="5" t="s">
         <v>1</v>
@@ -5784,13 +5733,13 @@
         <v>45785</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E198" s="5" t="s">
         <v>1</v>
@@ -5801,13 +5750,13 @@
         <v>45785</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>1</v>
@@ -5818,10 +5767,10 @@
         <v>45785</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>5</v>
@@ -5835,13 +5784,13 @@
         <v>45789</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>0</v>
@@ -5852,13 +5801,13 @@
         <v>45789</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E202" s="5" t="s">
         <v>1</v>
@@ -5869,13 +5818,13 @@
         <v>45789</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>1</v>
@@ -5886,13 +5835,13 @@
         <v>45789</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E204" s="5" t="s">
         <v>1</v>
@@ -5903,10 +5852,10 @@
         <v>45789</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>5</v>
@@ -5920,13 +5869,13 @@
         <v>45789</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E206" s="5" t="s">
         <v>1</v>
@@ -5937,13 +5886,13 @@
         <v>45789</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E207" s="5" t="s">
         <v>1</v>
@@ -5954,13 +5903,13 @@
         <v>45789</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E208" s="5" t="s">
         <v>0</v>
@@ -5971,13 +5920,13 @@
         <v>45790</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E209" s="5" t="s">
         <v>0</v>
@@ -5988,10 +5937,10 @@
         <v>45790</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>5</v>
@@ -6005,13 +5954,13 @@
         <v>45791</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E211" s="5" t="s">
         <v>0</v>
@@ -6025,7 +5974,7 @@
         <v>4</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>5</v>
@@ -6042,7 +5991,7 @@
         <v>4</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>5</v>
@@ -6059,7 +6008,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>5</v>
@@ -6073,13 +6022,13 @@
         <v>45792</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>108</v>
+        <v>554</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>0</v>
@@ -6093,10 +6042,10 @@
         <v>4</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E216" s="5" t="s">
         <v>0</v>
@@ -6107,13 +6056,13 @@
         <v>45792</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>108</v>
+        <v>554</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>0</v>
@@ -6127,10 +6076,10 @@
         <v>4</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E218" s="5" t="s">
         <v>0</v>
@@ -6144,10 +6093,10 @@
         <v>2</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>0</v>
@@ -6158,13 +6107,13 @@
         <v>45792</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>108</v>
+        <v>554</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>1</v>
@@ -6175,13 +6124,13 @@
         <v>45793</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>108</v>
+        <v>554</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>0</v>
@@ -6192,13 +6141,13 @@
         <v>45793</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>108</v>
+        <v>554</v>
       </c>
       <c r="E222" s="5" t="s">
         <v>1</v>
@@ -6212,10 +6161,10 @@
         <v>2</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E223" s="5" t="s">
         <v>1</v>
@@ -6229,7 +6178,7 @@
         <v>4</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>5</v>
@@ -6246,7 +6195,7 @@
         <v>4</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>5</v>
@@ -6263,7 +6212,7 @@
         <v>2</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>5</v>
@@ -6277,13 +6226,13 @@
         <v>45796</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E227" s="5" t="s">
         <v>0</v>
@@ -6297,7 +6246,7 @@
         <v>4</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D228" s="5" t="s">
         <v>5</v>
@@ -6311,10 +6260,10 @@
         <v>45796</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D229" s="5" t="s">
         <v>5</v>
@@ -6328,13 +6277,13 @@
         <v>45796</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>0</v>
@@ -6348,7 +6297,7 @@
         <v>4</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>5</v>
@@ -6362,13 +6311,13 @@
         <v>45797</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E232" s="5" t="s">
         <v>0</v>
@@ -6379,13 +6328,13 @@
         <v>45797</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E233" s="5" t="s">
         <v>1</v>
@@ -6396,13 +6345,13 @@
         <v>45797</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>1</v>
@@ -6413,10 +6362,10 @@
         <v>45798</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>5</v>
@@ -6430,13 +6379,13 @@
         <v>45800</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E236" s="5" t="s">
         <v>0</v>
@@ -6447,13 +6396,13 @@
         <v>45800</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E237" s="5" t="s">
         <v>0</v>
@@ -6464,13 +6413,13 @@
         <v>45803</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E238" s="5" t="s">
         <v>0</v>
@@ -6481,13 +6430,13 @@
         <v>45803</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>1</v>
@@ -6498,13 +6447,13 @@
         <v>45803</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E240" s="5" t="s">
         <v>0</v>
@@ -6515,10 +6464,10 @@
         <v>45803</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>5</v>
@@ -6532,13 +6481,13 @@
         <v>45804</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>1</v>
@@ -6549,13 +6498,13 @@
         <v>45804</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>1</v>
@@ -6566,13 +6515,13 @@
         <v>45804</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E244" s="5" t="s">
         <v>1</v>
@@ -6583,13 +6532,13 @@
         <v>45805</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E245" s="5" t="s">
         <v>1</v>
@@ -6600,13 +6549,13 @@
         <v>45807</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E246" s="5" t="s">
         <v>1</v>
@@ -6617,13 +6566,13 @@
         <v>45810</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>0</v>
@@ -6637,7 +6586,7 @@
         <v>4</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D248" s="5" t="s">
         <v>5</v>
@@ -6651,13 +6600,13 @@
         <v>45810</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E249" s="5" t="s">
         <v>1</v>
@@ -6668,13 +6617,13 @@
         <v>45812</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E250" s="5" t="s">
         <v>0</v>
@@ -6684,11 +6633,11 @@
       <c r="A251" s="4">
         <v>45812</v>
       </c>
-      <c r="B251" s="16" t="s">
-        <v>113</v>
+      <c r="B251" s="15" t="s">
+        <v>112</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>5</v>
@@ -6702,13 +6651,13 @@
         <v>45813</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E252" s="5" t="s">
         <v>0</v>
@@ -6719,13 +6668,13 @@
         <v>45813</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E253" s="5" t="s">
         <v>0</v>
@@ -6735,11 +6684,11 @@
       <c r="A254" s="4">
         <v>45813</v>
       </c>
-      <c r="B254" s="16" t="s">
-        <v>113</v>
+      <c r="B254" s="15" t="s">
+        <v>112</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D254" s="5" t="s">
         <v>5</v>
@@ -6753,13 +6702,13 @@
         <v>45813</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E255" s="5" t="s">
         <v>0</v>
@@ -6770,13 +6719,13 @@
         <v>45817</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E256" s="5" t="s">
         <v>0</v>
@@ -6787,10 +6736,10 @@
         <v>45817</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>5</v>
@@ -6807,7 +6756,7 @@
         <v>2</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>5</v>
@@ -6821,10 +6770,10 @@
         <v>45817</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D259" s="5" t="s">
         <v>5</v>
@@ -6838,13 +6787,13 @@
         <v>45818</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>0</v>
@@ -6858,7 +6807,7 @@
         <v>2</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D261" s="5" t="s">
         <v>5</v>
@@ -6872,13 +6821,13 @@
         <v>45819</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>0</v>
@@ -6892,7 +6841,7 @@
         <v>2</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>5</v>
@@ -6906,13 +6855,13 @@
         <v>45820</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>0</v>
@@ -6926,7 +6875,7 @@
         <v>4</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D265" s="5" t="s">
         <v>5</v>
@@ -6940,13 +6889,13 @@
         <v>45820</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>0</v>
@@ -6957,13 +6906,13 @@
         <v>45821</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E267" s="5" t="s">
         <v>1</v>
@@ -6974,13 +6923,13 @@
         <v>45821</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E268" s="5" t="s">
         <v>1</v>
@@ -6994,7 +6943,7 @@
         <v>2</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D269" s="5" t="s">
         <v>5</v>
@@ -7008,10 +6957,10 @@
         <v>45824</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D270" s="5" t="s">
         <v>5</v>
@@ -7024,11 +6973,11 @@
       <c r="A271" s="4">
         <v>45824</v>
       </c>
-      <c r="B271" s="17" t="s">
-        <v>286</v>
+      <c r="B271" s="16" t="s">
+        <v>285</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D271" s="5" t="s">
         <v>5</v>
@@ -7045,7 +6994,7 @@
         <v>4</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D272" s="5" t="s">
         <v>5</v>
@@ -7062,7 +7011,7 @@
         <v>4</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>5</v>
@@ -7076,13 +7025,13 @@
         <v>45825</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E274" s="5" t="s">
         <v>0</v>
@@ -7093,13 +7042,13 @@
         <v>45826</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>1</v>
@@ -7110,10 +7059,10 @@
         <v>45827</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D276" s="5" t="s">
         <v>5</v>
@@ -7130,7 +7079,7 @@
         <v>4</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D277" s="5" t="s">
         <v>5</v>
@@ -7144,13 +7093,13 @@
         <v>45831</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E278" s="5" t="s">
         <v>0</v>
@@ -7161,10 +7110,10 @@
         <v>45831</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D279" s="5" t="s">
         <v>5</v>
@@ -7178,10 +7127,10 @@
         <v>45831</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D280" s="5" t="s">
         <v>5</v>
@@ -7195,13 +7144,13 @@
         <v>45832</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>0</v>
@@ -7212,13 +7161,13 @@
         <v>45833</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>0</v>
@@ -7229,13 +7178,13 @@
         <v>45833</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>0</v>
@@ -7246,10 +7195,10 @@
         <v>45833</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D284" s="5" t="s">
         <v>5</v>
@@ -7263,10 +7212,10 @@
         <v>45833</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D285" s="5" t="s">
         <v>5</v>
@@ -7280,10 +7229,10 @@
         <v>45834</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D286" s="5" t="s">
         <v>5</v>
@@ -7297,13 +7246,13 @@
         <v>45834</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>0</v>
@@ -7314,13 +7263,13 @@
         <v>45832</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>5</v>
+        <v>554</v>
       </c>
       <c r="E288" s="5" t="s">
         <v>0</v>
@@ -7331,10 +7280,10 @@
         <v>45835</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D289" s="5" t="s">
         <v>5</v>
@@ -7348,10 +7297,10 @@
         <v>45835</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D290" s="5" t="s">
         <v>5</v>
@@ -7368,10 +7317,10 @@
         <v>4</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E291" s="5" t="s">
         <v>1</v>
@@ -7382,10 +7331,10 @@
         <v>45838</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D292" s="5" t="s">
         <v>5</v>
@@ -7399,10 +7348,10 @@
         <v>45841</v>
       </c>
       <c r="B293" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C293" s="6" t="s">
         <v>332</v>
-      </c>
-      <c r="C293" s="6" t="s">
-        <v>333</v>
       </c>
       <c r="D293" s="5" t="s">
         <v>5</v>
@@ -7416,10 +7365,10 @@
         <v>45862</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D294" s="5" t="s">
         <v>5</v>
@@ -7436,7 +7385,7 @@
         <v>4</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D295" s="5" t="s">
         <v>5</v>
@@ -7453,10 +7402,10 @@
         <v>4</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="D296" s="16" t="s">
-        <v>422</v>
+        <v>339</v>
+      </c>
+      <c r="D296" s="15" t="s">
+        <v>421</v>
       </c>
       <c r="E296" s="5" t="s">
         <v>1</v>
@@ -7467,13 +7416,13 @@
         <v>45870</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="D297" s="16" t="s">
-        <v>422</v>
+        <v>340</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>1</v>
@@ -7484,13 +7433,13 @@
         <v>45870</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="D298" s="16" t="s">
-        <v>422</v>
+        <v>341</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E298" s="5" t="s">
         <v>0</v>
@@ -7501,13 +7450,13 @@
         <v>45870</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="D299" s="16" t="s">
-        <v>109</v>
+        <v>342</v>
+      </c>
+      <c r="D299" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E299" s="5" t="s">
         <v>0</v>
@@ -7521,10 +7470,10 @@
         <v>4</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D300" s="18" t="s">
-        <v>423</v>
+        <v>343</v>
+      </c>
+      <c r="D300" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>1</v>
@@ -7535,13 +7484,13 @@
         <v>45870</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="D301" s="16" t="s">
-        <v>109</v>
+        <v>344</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E301" s="5" t="s">
         <v>1</v>
@@ -7555,10 +7504,10 @@
         <v>2</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="D302" s="16" t="s">
-        <v>109</v>
+        <v>345</v>
+      </c>
+      <c r="D302" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E302" s="5" t="s">
         <v>0</v>
@@ -7572,10 +7521,10 @@
         <v>4</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D303" s="19" t="s">
-        <v>424</v>
+        <v>346</v>
+      </c>
+      <c r="D303" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E303" s="5" t="s">
         <v>0</v>
@@ -7589,10 +7538,10 @@
         <v>4</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="D304" s="18" t="s">
-        <v>423</v>
+        <v>347</v>
+      </c>
+      <c r="D304" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E304" s="5" t="s">
         <v>1</v>
@@ -7606,10 +7555,10 @@
         <v>4</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="D305" s="18" t="s">
-        <v>423</v>
+        <v>348</v>
+      </c>
+      <c r="D305" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E305" s="5" t="s">
         <v>1</v>
@@ -7623,10 +7572,10 @@
         <v>4</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="D306" s="18" t="s">
-        <v>423</v>
+        <v>349</v>
+      </c>
+      <c r="D306" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E306" s="5" t="s">
         <v>1</v>
@@ -7640,10 +7589,10 @@
         <v>4</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="D307" s="18" t="s">
-        <v>423</v>
+        <v>350</v>
+      </c>
+      <c r="D307" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E307" s="5" t="s">
         <v>1</v>
@@ -7657,10 +7606,10 @@
         <v>4</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="D308" s="18" t="s">
-        <v>423</v>
+        <v>351</v>
+      </c>
+      <c r="D308" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E308" s="5" t="s">
         <v>1</v>
@@ -7674,10 +7623,10 @@
         <v>4</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="D309" s="18" t="s">
-        <v>423</v>
+        <v>352</v>
+      </c>
+      <c r="D309" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E309" s="5" t="s">
         <v>1</v>
@@ -7691,10 +7640,10 @@
         <v>4</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D310" s="18" t="s">
-        <v>423</v>
+        <v>353</v>
+      </c>
+      <c r="D310" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E310" s="5" t="s">
         <v>1</v>
@@ -7708,10 +7657,10 @@
         <v>4</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D311" s="18" t="s">
-        <v>423</v>
+        <v>353</v>
+      </c>
+      <c r="D311" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E311" s="5" t="s">
         <v>1</v>
@@ -7725,10 +7674,10 @@
         <v>4</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="D312" s="18" t="s">
-        <v>423</v>
+        <v>354</v>
+      </c>
+      <c r="D312" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E312" s="5" t="s">
         <v>1</v>
@@ -7739,13 +7688,13 @@
         <v>45873</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="D313" s="16" t="s">
-        <v>109</v>
+        <v>355</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E313" s="5" t="s">
         <v>0</v>
@@ -7759,10 +7708,10 @@
         <v>4</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="D314" s="18" t="s">
-        <v>423</v>
+        <v>356</v>
+      </c>
+      <c r="D314" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E314" s="5" t="s">
         <v>1</v>
@@ -7773,13 +7722,13 @@
         <v>45873</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="D315" s="16" t="s">
-        <v>109</v>
+        <v>357</v>
+      </c>
+      <c r="D315" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E315" s="5" t="s">
         <v>1</v>
@@ -7790,13 +7739,13 @@
         <v>45873</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="D316" s="16" t="s">
-        <v>422</v>
+        <v>358</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E316" s="5" t="s">
         <v>1</v>
@@ -7807,13 +7756,13 @@
         <v>45874</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="D317" s="16" t="s">
-        <v>109</v>
+        <v>359</v>
+      </c>
+      <c r="D317" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E317" s="5" t="s">
         <v>0</v>
@@ -7824,13 +7773,13 @@
         <v>45874</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D318" s="16" t="s">
-        <v>109</v>
+        <v>360</v>
+      </c>
+      <c r="D318" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E318" s="5" t="s">
         <v>0</v>
@@ -7841,13 +7790,13 @@
         <v>45874</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="D319" s="16" t="s">
-        <v>109</v>
+        <v>361</v>
+      </c>
+      <c r="D319" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E319" s="5" t="s">
         <v>0</v>
@@ -7858,13 +7807,13 @@
         <v>45874</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="D320" s="16" t="s">
-        <v>109</v>
+        <v>362</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E320" s="5" t="s">
         <v>0</v>
@@ -7875,13 +7824,13 @@
         <v>45875</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="D321" s="16" t="s">
-        <v>109</v>
+        <v>363</v>
+      </c>
+      <c r="D321" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E321" s="5" t="s">
         <v>1</v>
@@ -7892,13 +7841,13 @@
         <v>45875</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="D322" s="16" t="s">
-        <v>109</v>
+        <v>364</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E322" s="5" t="s">
         <v>0</v>
@@ -7909,13 +7858,13 @@
         <v>45875</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D323" s="16" t="s">
-        <v>109</v>
+        <v>365</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E323" s="5" t="s">
         <v>0</v>
@@ -7926,13 +7875,13 @@
         <v>45875</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D324" s="16" t="s">
-        <v>109</v>
+        <v>365</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E324" s="5" t="s">
         <v>0</v>
@@ -7946,10 +7895,10 @@
         <v>4</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="D325" s="16" t="s">
-        <v>109</v>
+        <v>366</v>
+      </c>
+      <c r="D325" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>0</v>
@@ -7963,10 +7912,10 @@
         <v>4</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="D326" s="16" t="s">
-        <v>109</v>
+        <v>366</v>
+      </c>
+      <c r="D326" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E326" s="5" t="s">
         <v>0</v>
@@ -7980,10 +7929,10 @@
         <v>4</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D327" s="16" t="s">
-        <v>109</v>
+        <v>367</v>
+      </c>
+      <c r="D327" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E327" s="5" t="s">
         <v>0</v>
@@ -7994,13 +7943,13 @@
         <v>45876</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D328" s="16" t="s">
-        <v>109</v>
+        <v>368</v>
+      </c>
+      <c r="D328" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E328" s="5" t="s">
         <v>0</v>
@@ -8011,13 +7960,13 @@
         <v>45877</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D329" s="16" t="s">
-        <v>109</v>
+        <v>369</v>
+      </c>
+      <c r="D329" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E329" s="5" t="s">
         <v>1</v>
@@ -8031,10 +7980,10 @@
         <v>4</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D330" s="16" t="s">
-        <v>109</v>
+        <v>370</v>
+      </c>
+      <c r="D330" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E330" s="5" t="s">
         <v>0</v>
@@ -8045,13 +7994,13 @@
         <v>45880</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="D331" s="16" t="s">
-        <v>109</v>
+        <v>371</v>
+      </c>
+      <c r="D331" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E331" s="5" t="s">
         <v>0</v>
@@ -8062,13 +8011,13 @@
         <v>45880</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D332" s="16" t="s">
-        <v>109</v>
+        <v>324</v>
+      </c>
+      <c r="D332" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E332" s="5" t="s">
         <v>1</v>
@@ -8082,10 +8031,10 @@
         <v>4</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="D333" s="16" t="s">
-        <v>109</v>
+        <v>372</v>
+      </c>
+      <c r="D333" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E333" s="5" t="s">
         <v>0</v>
@@ -8096,13 +8045,13 @@
         <v>45880</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="D334" s="16" t="s">
-        <v>109</v>
+        <v>373</v>
+      </c>
+      <c r="D334" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E334" s="5" t="s">
         <v>0</v>
@@ -8116,10 +8065,10 @@
         <v>2</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="D335" s="16" t="s">
-        <v>109</v>
+        <v>374</v>
+      </c>
+      <c r="D335" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E335" s="5" t="s">
         <v>0</v>
@@ -8133,10 +8082,10 @@
         <v>2</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="D336" s="16" t="s">
-        <v>109</v>
+        <v>375</v>
+      </c>
+      <c r="D336" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E336" s="5" t="s">
         <v>0</v>
@@ -8147,13 +8096,13 @@
         <v>45882</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D337" s="16" t="s">
-        <v>422</v>
+        <v>376</v>
+      </c>
+      <c r="D337" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E337" s="5" t="s">
         <v>1</v>
@@ -8164,13 +8113,13 @@
         <v>45882</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="D338" s="16" t="s">
-        <v>109</v>
+        <v>377</v>
+      </c>
+      <c r="D338" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E338" s="5" t="s">
         <v>0</v>
@@ -8181,13 +8130,13 @@
         <v>45882</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="D339" s="16" t="s">
-        <v>109</v>
+        <v>378</v>
+      </c>
+      <c r="D339" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E339" s="5" t="s">
         <v>0</v>
@@ -8198,13 +8147,13 @@
         <v>45883</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="D340" s="16" t="s">
-        <v>109</v>
+        <v>379</v>
+      </c>
+      <c r="D340" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E340" s="5" t="s">
         <v>0</v>
@@ -8215,13 +8164,13 @@
         <v>45887</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D341" s="16" t="s">
-        <v>109</v>
+        <v>380</v>
+      </c>
+      <c r="D341" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E341" s="5" t="s">
         <v>0</v>
@@ -8232,13 +8181,13 @@
         <v>45888</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="D342" s="16" t="s">
-        <v>109</v>
+        <v>381</v>
+      </c>
+      <c r="D342" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E342" s="5" t="s">
         <v>0</v>
@@ -8249,13 +8198,13 @@
         <v>45888</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="D343" s="16" t="s">
-        <v>109</v>
+        <v>382</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E343" s="5" t="s">
         <v>0</v>
@@ -8266,13 +8215,13 @@
         <v>45889</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="D344" s="16" t="s">
-        <v>109</v>
+        <v>383</v>
+      </c>
+      <c r="D344" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E344" s="5" t="s">
         <v>1</v>
@@ -8283,13 +8232,13 @@
         <v>45889</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="D345" s="16" t="s">
-        <v>109</v>
+        <v>384</v>
+      </c>
+      <c r="D345" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E345" s="5" t="s">
         <v>1</v>
@@ -8300,13 +8249,13 @@
         <v>45889</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="D346" s="16" t="s">
-        <v>109</v>
+        <v>385</v>
+      </c>
+      <c r="D346" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E346" s="5" t="s">
         <v>0</v>
@@ -8317,13 +8266,13 @@
         <v>45889</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="D347" s="16" t="s">
-        <v>109</v>
+        <v>386</v>
+      </c>
+      <c r="D347" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E347" s="5" t="s">
         <v>6</v>
@@ -8337,10 +8286,10 @@
         <v>4</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="D348" s="18" t="s">
-        <v>423</v>
+        <v>387</v>
+      </c>
+      <c r="D348" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E348" s="5" t="s">
         <v>1</v>
@@ -8354,10 +8303,10 @@
         <v>2</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D349" s="16" t="s">
-        <v>109</v>
+        <v>388</v>
+      </c>
+      <c r="D349" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E349" s="5" t="s">
         <v>1</v>
@@ -8368,13 +8317,13 @@
         <v>45890</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="D350" s="16" t="s">
-        <v>109</v>
+        <v>389</v>
+      </c>
+      <c r="D350" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E350" s="5" t="s">
         <v>0</v>
@@ -8385,13 +8334,13 @@
         <v>45890</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="D351" s="16" t="s">
-        <v>109</v>
+        <v>390</v>
+      </c>
+      <c r="D351" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E351" s="5" t="s">
         <v>1</v>
@@ -8402,13 +8351,13 @@
         <v>45890</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="D352" s="16" t="s">
-        <v>109</v>
+        <v>391</v>
+      </c>
+      <c r="D352" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E352" s="5" t="s">
         <v>0</v>
@@ -8419,13 +8368,13 @@
         <v>45890</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="D353" s="16" t="s">
-        <v>109</v>
+        <v>392</v>
+      </c>
+      <c r="D353" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E353" s="5" t="s">
         <v>0</v>
@@ -8439,10 +8388,10 @@
         <v>4</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="D354" s="18" t="s">
-        <v>423</v>
+        <v>393</v>
+      </c>
+      <c r="D354" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E354" s="5" t="s">
         <v>1</v>
@@ -8453,13 +8402,13 @@
         <v>45891</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="D355" s="16" t="s">
-        <v>109</v>
+        <v>394</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E355" s="5" t="s">
         <v>0</v>
@@ -8470,13 +8419,13 @@
         <v>45891</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="D356" s="16" t="s">
-        <v>109</v>
+        <v>395</v>
+      </c>
+      <c r="D356" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E356" s="5" t="s">
         <v>1</v>
@@ -8487,13 +8436,13 @@
         <v>45891</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="D357" s="16" t="s">
-        <v>109</v>
+        <v>396</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E357" s="5" t="s">
         <v>0</v>
@@ -8504,13 +8453,13 @@
         <v>45894</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="D358" s="16" t="s">
-        <v>109</v>
+        <v>397</v>
+      </c>
+      <c r="D358" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E358" s="5" t="s">
         <v>0</v>
@@ -8521,13 +8470,13 @@
         <v>45894</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D359" s="16" t="s">
-        <v>109</v>
+        <v>398</v>
+      </c>
+      <c r="D359" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E359" s="5" t="s">
         <v>1</v>
@@ -8538,13 +8487,13 @@
         <v>45894</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="D360" s="16" t="s">
-        <v>109</v>
+        <v>399</v>
+      </c>
+      <c r="D360" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E360" s="5" t="s">
         <v>0</v>
@@ -8558,10 +8507,10 @@
         <v>4</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="D361" s="18" t="s">
-        <v>423</v>
+        <v>400</v>
+      </c>
+      <c r="D361" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E361" s="5" t="s">
         <v>1</v>
@@ -8572,13 +8521,13 @@
         <v>45894</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="D362" s="16" t="s">
-        <v>109</v>
+        <v>401</v>
+      </c>
+      <c r="D362" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E362" s="5" t="s">
         <v>0</v>
@@ -8589,13 +8538,13 @@
         <v>45894</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="D363" s="16" t="s">
-        <v>109</v>
+        <v>402</v>
+      </c>
+      <c r="D363" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E363" s="5" t="s">
         <v>0</v>
@@ -8609,10 +8558,10 @@
         <v>2</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="D364" s="16" t="s">
-        <v>109</v>
+        <v>403</v>
+      </c>
+      <c r="D364" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E364" s="5" t="s">
         <v>0</v>
@@ -8623,13 +8572,13 @@
         <v>45895</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D365" s="16" t="s">
-        <v>109</v>
+        <v>404</v>
+      </c>
+      <c r="D365" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E365" s="5" t="s">
         <v>1</v>
@@ -8643,10 +8592,10 @@
         <v>4</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="D366" s="18" t="s">
-        <v>423</v>
+        <v>405</v>
+      </c>
+      <c r="D366" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E366" s="5" t="s">
         <v>1</v>
@@ -8657,13 +8606,13 @@
         <v>45896</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D367" s="16" t="s">
-        <v>425</v>
+        <v>406</v>
+      </c>
+      <c r="D367" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E367" s="5" t="s">
         <v>0</v>
@@ -8674,13 +8623,13 @@
         <v>45896</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="D368" s="16" t="s">
-        <v>109</v>
+        <v>407</v>
+      </c>
+      <c r="D368" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E368" s="5" t="s">
         <v>1</v>
@@ -8691,13 +8640,13 @@
         <v>45896</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="D369" s="16" t="s">
-        <v>109</v>
+        <v>408</v>
+      </c>
+      <c r="D369" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E369" s="5" t="s">
         <v>1</v>
@@ -8708,13 +8657,13 @@
         <v>45896</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="D370" s="16" t="s">
-        <v>109</v>
+        <v>409</v>
+      </c>
+      <c r="D370" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E370" s="5" t="s">
         <v>0</v>
@@ -8728,10 +8677,10 @@
         <v>4</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D371" s="16" t="s">
-        <v>109</v>
+        <v>410</v>
+      </c>
+      <c r="D371" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E371" s="5" t="s">
         <v>0</v>
@@ -8745,10 +8694,10 @@
         <v>4</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="D372" s="16" t="s">
-        <v>109</v>
+        <v>411</v>
+      </c>
+      <c r="D372" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E372" s="5" t="s">
         <v>0</v>
@@ -8759,13 +8708,13 @@
         <v>45897</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="D373" s="16" t="s">
-        <v>109</v>
+        <v>412</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E373" s="5" t="s">
         <v>1</v>
@@ -8776,13 +8725,13 @@
         <v>45897</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="D374" s="16" t="s">
-        <v>109</v>
+        <v>413</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E374" s="5" t="s">
         <v>1</v>
@@ -8793,13 +8742,13 @@
         <v>45897</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D375" s="16" t="s">
-        <v>109</v>
+        <v>414</v>
+      </c>
+      <c r="D375" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E375" s="5" t="s">
         <v>0</v>
@@ -8810,13 +8759,13 @@
         <v>45897</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="D376" s="16" t="s">
-        <v>109</v>
+        <v>415</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E376" s="5" t="s">
         <v>0</v>
@@ -8827,13 +8776,13 @@
         <v>45898</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="D377" s="16" t="s">
-        <v>109</v>
+        <v>416</v>
+      </c>
+      <c r="D377" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E377" s="5" t="s">
         <v>1</v>
@@ -8844,13 +8793,13 @@
         <v>45898</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="D378" s="16" t="s">
-        <v>109</v>
+        <v>417</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E378" s="5" t="s">
         <v>0</v>
@@ -8864,10 +8813,10 @@
         <v>4</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="D379" s="16" t="s">
-        <v>109</v>
+        <v>418</v>
+      </c>
+      <c r="D379" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E379" s="5" t="s">
         <v>0</v>
@@ -8878,13 +8827,13 @@
         <v>45898</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D380" s="16" t="s">
-        <v>109</v>
+        <v>419</v>
+      </c>
+      <c r="D380" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E380" s="5" t="s">
         <v>0</v>
@@ -8895,13 +8844,13 @@
         <v>45898</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="D381" s="16" t="s">
-        <v>109</v>
+        <v>420</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E381" s="5" t="s">
         <v>0</v>
@@ -8912,10 +8861,10 @@
         <v>45901</v>
       </c>
       <c r="B382" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D382" s="10" t="s">
         <v>5</v>
@@ -8929,10 +8878,10 @@
         <v>45901</v>
       </c>
       <c r="B383" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D383" s="10" t="s">
         <v>5</v>
@@ -8946,13 +8895,13 @@
         <v>45901</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="D384" s="10" t="s">
-        <v>5</v>
+        <v>425</v>
+      </c>
+      <c r="D384" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E384" s="8" t="s">
         <v>0</v>
@@ -8963,13 +8912,13 @@
         <v>45901</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C385" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="D385" s="10" t="s">
-        <v>5</v>
+        <v>426</v>
+      </c>
+      <c r="D385" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E385" s="8" t="s">
         <v>0</v>
@@ -8980,13 +8929,13 @@
         <v>45902</v>
       </c>
       <c r="B386" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="D386" s="10" t="s">
-        <v>5</v>
+        <v>360</v>
+      </c>
+      <c r="D386" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E386" s="8" t="s">
         <v>0</v>
@@ -8997,13 +8946,13 @@
         <v>45902</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C387" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="D387" s="10" t="s">
-        <v>5</v>
+        <v>427</v>
+      </c>
+      <c r="D387" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E387" s="8" t="s">
         <v>1</v>
@@ -9014,13 +8963,13 @@
         <v>45902</v>
       </c>
       <c r="B388" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C388" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="D388" s="10" t="s">
-        <v>5</v>
+        <v>428</v>
+      </c>
+      <c r="D388" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E388" s="8" t="s">
         <v>0</v>
@@ -9034,10 +8983,10 @@
         <v>4</v>
       </c>
       <c r="C389" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="D389" s="10" t="s">
-        <v>423</v>
+        <v>429</v>
+      </c>
+      <c r="D389" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E389" s="8" t="s">
         <v>0</v>
@@ -9048,10 +8997,10 @@
         <v>45904</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C390" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D390" s="10" t="s">
         <v>5</v>
@@ -9068,10 +9017,10 @@
         <v>4</v>
       </c>
       <c r="C391" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="D391" s="10" t="s">
-        <v>5</v>
+        <v>431</v>
+      </c>
+      <c r="D391" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E391" s="8" t="s">
         <v>0</v>
@@ -9082,13 +9031,13 @@
         <v>45905</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C392" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="D392" s="10" t="s">
-        <v>5</v>
+        <v>432</v>
+      </c>
+      <c r="D392" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E392" s="8" t="s">
         <v>0</v>
@@ -9102,7 +9051,7 @@
         <v>2</v>
       </c>
       <c r="C393" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D393" s="10" t="s">
         <v>5</v>
@@ -9119,10 +9068,10 @@
         <v>4</v>
       </c>
       <c r="C394" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="D394" s="10" t="s">
-        <v>8</v>
+        <v>434</v>
+      </c>
+      <c r="D394" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E394" s="8" t="s">
         <v>1</v>
@@ -9133,13 +9082,13 @@
         <v>45908</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C395" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="D395" s="10" t="s">
-        <v>5</v>
+        <v>435</v>
+      </c>
+      <c r="D395" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E395" s="8" t="s">
         <v>1</v>
@@ -9150,10 +9099,10 @@
         <v>45908</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C396" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D396" s="10" t="s">
         <v>5</v>
@@ -9167,13 +9116,13 @@
         <v>45908</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C397" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D397" s="10" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E397" s="8" t="s">
         <v>0</v>
@@ -9184,13 +9133,13 @@
         <v>45908</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C398" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="D398" s="10" t="s">
-        <v>5</v>
+        <v>360</v>
+      </c>
+      <c r="D398" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E398" s="8" t="s">
         <v>1</v>
@@ -9204,10 +9153,10 @@
         <v>4</v>
       </c>
       <c r="C399" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="D399" s="10" t="s">
-        <v>8</v>
+        <v>438</v>
+      </c>
+      <c r="D399" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E399" s="8" t="s">
         <v>1</v>
@@ -9221,10 +9170,10 @@
         <v>4</v>
       </c>
       <c r="C400" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="D400" s="10" t="s">
-        <v>8</v>
+        <v>438</v>
+      </c>
+      <c r="D400" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E400" s="8" t="s">
         <v>1</v>
@@ -9235,13 +9184,13 @@
         <v>45908</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C401" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="D401" s="10" t="s">
-        <v>5</v>
+        <v>439</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E401" s="8" t="s">
         <v>0</v>
@@ -9255,10 +9204,10 @@
         <v>4</v>
       </c>
       <c r="C402" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="D402" s="10" t="s">
-        <v>8</v>
+        <v>440</v>
+      </c>
+      <c r="D402" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E402" s="8" t="s">
         <v>1</v>
@@ -9269,10 +9218,10 @@
         <v>45908</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C403" s="9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D403" s="10" t="s">
         <v>5</v>
@@ -9286,10 +9235,10 @@
         <v>45909</v>
       </c>
       <c r="B404" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C404" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D404" s="10" t="s">
         <v>5</v>
@@ -9306,10 +9255,10 @@
         <v>4</v>
       </c>
       <c r="C405" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="D405" s="10" t="s">
-        <v>8</v>
+        <v>443</v>
+      </c>
+      <c r="D405" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E405" s="8" t="s">
         <v>1</v>
@@ -9323,10 +9272,10 @@
         <v>4</v>
       </c>
       <c r="C406" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="D406" s="10" t="s">
-        <v>8</v>
+        <v>444</v>
+      </c>
+      <c r="D406" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E406" s="8" t="s">
         <v>1</v>
@@ -9340,10 +9289,10 @@
         <v>4</v>
       </c>
       <c r="C407" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D407" s="10" t="s">
-        <v>5</v>
+        <v>254</v>
+      </c>
+      <c r="D407" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E407" s="8" t="s">
         <v>1</v>
@@ -9357,10 +9306,10 @@
         <v>4</v>
       </c>
       <c r="C408" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D408" s="10" t="s">
-        <v>5</v>
+        <v>445</v>
+      </c>
+      <c r="D408" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E408" s="8" t="s">
         <v>0</v>
@@ -9374,10 +9323,10 @@
         <v>4</v>
       </c>
       <c r="C409" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="D409" s="10" t="s">
-        <v>5</v>
+        <v>446</v>
+      </c>
+      <c r="D409" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E409" s="8" t="s">
         <v>0</v>
@@ -9388,13 +9337,13 @@
         <v>45915</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="D410" s="10" t="s">
-        <v>5</v>
+        <v>447</v>
+      </c>
+      <c r="D410" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E410" s="8" t="s">
         <v>0</v>
@@ -9405,13 +9354,13 @@
         <v>45916</v>
       </c>
       <c r="B411" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C411" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="D411" s="10" t="s">
-        <v>5</v>
+        <v>448</v>
+      </c>
+      <c r="D411" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E411" s="8" t="s">
         <v>0</v>
@@ -9422,13 +9371,13 @@
         <v>45919</v>
       </c>
       <c r="B412" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C412" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D412" s="10" t="s">
-        <v>5</v>
+        <v>449</v>
+      </c>
+      <c r="D412" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E412" s="8" t="s">
         <v>0</v>
@@ -9439,10 +9388,10 @@
         <v>45922</v>
       </c>
       <c r="B413" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C413" s="9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D413" s="10" t="s">
         <v>5</v>
@@ -9456,13 +9405,13 @@
         <v>45922</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C414" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="D414" s="10" t="s">
-        <v>5</v>
+        <v>451</v>
+      </c>
+      <c r="D414" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E414" s="8" t="s">
         <v>0</v>
@@ -9473,13 +9422,13 @@
         <v>45922</v>
       </c>
       <c r="B415" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C415" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="D415" s="10" t="s">
-        <v>5</v>
+        <v>447</v>
+      </c>
+      <c r="D415" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E415" s="8" t="s">
         <v>1</v>
@@ -9490,10 +9439,10 @@
         <v>45923</v>
       </c>
       <c r="B416" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C416" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D416" s="10" t="s">
         <v>5</v>
@@ -9507,10 +9456,10 @@
         <v>45923</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C417" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D417" s="10" t="s">
         <v>5</v>
@@ -9524,13 +9473,13 @@
         <v>45925</v>
       </c>
       <c r="B418" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C418" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="D418" s="10" t="s">
-        <v>5</v>
+        <v>454</v>
+      </c>
+      <c r="D418" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E418" s="8" t="s">
         <v>0</v>
@@ -9544,10 +9493,10 @@
         <v>4</v>
       </c>
       <c r="C419" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="D419" s="10" t="s">
-        <v>423</v>
+        <v>455</v>
+      </c>
+      <c r="D419" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E419" s="8" t="s">
         <v>0</v>
@@ -9561,10 +9510,10 @@
         <v>4</v>
       </c>
       <c r="C420" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D420" s="10" t="s">
-        <v>423</v>
+        <v>456</v>
+      </c>
+      <c r="D420" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E420" s="8" t="s">
         <v>1</v>
@@ -9575,10 +9524,10 @@
         <v>45929</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C421" s="9" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D421" s="10" t="s">
         <v>5</v>
@@ -9595,10 +9544,10 @@
         <v>4</v>
       </c>
       <c r="C422" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="D422" s="10" t="s">
-        <v>423</v>
+        <v>458</v>
+      </c>
+      <c r="D422" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E422" s="8" t="s">
         <v>1</v>
@@ -9612,10 +9561,10 @@
         <v>4</v>
       </c>
       <c r="C423" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="D423" s="10" t="s">
-        <v>8</v>
+        <v>459</v>
+      </c>
+      <c r="D423" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E423" s="8" t="s">
         <v>1</v>
@@ -9629,10 +9578,10 @@
         <v>4</v>
       </c>
       <c r="C424" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="D424" s="10" t="s">
-        <v>8</v>
+        <v>460</v>
+      </c>
+      <c r="D424" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E424" s="8" t="s">
         <v>1</v>
@@ -9646,10 +9595,10 @@
         <v>4</v>
       </c>
       <c r="C425" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="D425" s="10" t="s">
-        <v>8</v>
+        <v>461</v>
+      </c>
+      <c r="D425" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E425" s="8" t="s">
         <v>1</v>
@@ -9663,10 +9612,10 @@
         <v>4</v>
       </c>
       <c r="C426" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="D426" s="10" t="s">
-        <v>8</v>
+        <v>462</v>
+      </c>
+      <c r="D426" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E426" s="8" t="s">
         <v>1</v>
@@ -9677,10 +9626,10 @@
         <v>45930</v>
       </c>
       <c r="B427" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C427" s="9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D427" s="10" t="s">
         <v>5</v>
@@ -9694,10 +9643,10 @@
         <v>45930</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C428" s="9" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D428" s="10" t="s">
         <v>5</v>
@@ -9711,13 +9660,13 @@
         <v>45930</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C429" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="D429" s="10" t="s">
-        <v>5</v>
+        <v>465</v>
+      </c>
+      <c r="D429" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E429" s="8" t="s">
         <v>0</v>
@@ -9728,10 +9677,10 @@
         <v>45931</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C430" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D430" s="10" t="s">
         <v>5</v>
@@ -9748,10 +9697,10 @@
         <v>4</v>
       </c>
       <c r="C431" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="D431" s="10" t="s">
-        <v>5</v>
+        <v>468</v>
+      </c>
+      <c r="D431" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E431" s="8" t="s">
         <v>0</v>
@@ -9762,13 +9711,13 @@
         <v>45940</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C432" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="D432" s="10" t="s">
-        <v>5</v>
+        <v>469</v>
+      </c>
+      <c r="D432" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E432" s="8" t="s">
         <v>0</v>
@@ -9779,10 +9728,10 @@
         <v>45940</v>
       </c>
       <c r="B433" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C433" s="9" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D433" s="10" t="s">
         <v>5</v>
@@ -9796,10 +9745,10 @@
         <v>45940</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C434" s="9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D434" s="10" t="s">
         <v>5</v>
@@ -9813,10 +9762,10 @@
         <v>45943</v>
       </c>
       <c r="B435" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C435" s="9" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D435" s="10" t="s">
         <v>5</v>
@@ -9833,7 +9782,7 @@
         <v>2</v>
       </c>
       <c r="C436" s="9" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D436" s="10" t="s">
         <v>5</v>
@@ -9847,10 +9796,10 @@
         <v>45943</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C437" s="9" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D437" s="10" t="s">
         <v>5</v>
@@ -9864,13 +9813,13 @@
         <v>45943</v>
       </c>
       <c r="B438" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C438" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="D438" s="10" t="s">
-        <v>5</v>
+        <v>475</v>
+      </c>
+      <c r="D438" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E438" s="8" t="s">
         <v>0</v>
@@ -9884,10 +9833,10 @@
         <v>4</v>
       </c>
       <c r="C439" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="D439" s="10" t="s">
-        <v>5</v>
+        <v>476</v>
+      </c>
+      <c r="D439" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E439" s="8" t="s">
         <v>0</v>
@@ -9898,10 +9847,10 @@
         <v>45943</v>
       </c>
       <c r="B440" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C440" s="9" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D440" s="10" t="s">
         <v>5</v>
@@ -9915,10 +9864,10 @@
         <v>45944</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C441" s="9" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D441" s="10" t="s">
         <v>5</v>
@@ -9932,13 +9881,13 @@
         <v>45945</v>
       </c>
       <c r="B442" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C442" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="D442" s="10" t="s">
-        <v>5</v>
+        <v>479</v>
+      </c>
+      <c r="D442" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E442" s="8" t="s">
         <v>0</v>
@@ -9952,10 +9901,10 @@
         <v>4</v>
       </c>
       <c r="C443" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="D443" s="10" t="s">
-        <v>5</v>
+        <v>480</v>
+      </c>
+      <c r="D443" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E443" s="8" t="s">
         <v>0</v>
@@ -9966,13 +9915,13 @@
         <v>45945</v>
       </c>
       <c r="B444" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C444" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="D444" s="10" t="s">
-        <v>5</v>
+        <v>481</v>
+      </c>
+      <c r="D444" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E444" s="8" t="s">
         <v>7</v>
@@ -9983,10 +9932,10 @@
         <v>45946</v>
       </c>
       <c r="B445" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C445" s="9" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D445" s="10" t="s">
         <v>5</v>
@@ -10000,10 +9949,10 @@
         <v>45943</v>
       </c>
       <c r="B446" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C446" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D446" s="10" t="s">
         <v>5</v>
@@ -10017,10 +9966,10 @@
         <v>45947</v>
       </c>
       <c r="B447" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C447" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D447" s="10" t="s">
         <v>5</v>
@@ -10034,13 +9983,13 @@
         <v>45950</v>
       </c>
       <c r="B448" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C448" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="D448" s="10" t="s">
-        <v>5</v>
+        <v>485</v>
+      </c>
+      <c r="D448" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E448" s="8" t="s">
         <v>0</v>
@@ -10051,10 +10000,10 @@
         <v>45951</v>
       </c>
       <c r="B449" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C449" s="9" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D449" s="10" t="s">
         <v>5</v>
@@ -10068,13 +10017,13 @@
         <v>45952</v>
       </c>
       <c r="B450" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C450" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="D450" s="10" t="s">
-        <v>5</v>
+        <v>487</v>
+      </c>
+      <c r="D450" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E450" s="8" t="s">
         <v>0</v>
@@ -10085,13 +10034,13 @@
         <v>45953</v>
       </c>
       <c r="B451" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C451" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="D451" s="10" t="s">
-        <v>5</v>
+        <v>488</v>
+      </c>
+      <c r="D451" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E451" s="8" t="s">
         <v>3</v>
@@ -10105,10 +10054,10 @@
         <v>4</v>
       </c>
       <c r="C452" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="D452" s="10" t="s">
-        <v>5</v>
+        <v>489</v>
+      </c>
+      <c r="D452" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E452" s="8" t="s">
         <v>0</v>
@@ -10122,10 +10071,10 @@
         <v>4</v>
       </c>
       <c r="C453" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="D453" s="10" t="s">
-        <v>8</v>
+        <v>490</v>
+      </c>
+      <c r="D453" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E453" s="8" t="s">
         <v>0</v>
@@ -10139,10 +10088,10 @@
         <v>4</v>
       </c>
       <c r="C454" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="D454" s="10" t="s">
-        <v>8</v>
+        <v>491</v>
+      </c>
+      <c r="D454" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E454" s="8" t="s">
         <v>1</v>
@@ -10153,10 +10102,10 @@
         <v>45957</v>
       </c>
       <c r="B455" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C455" s="9" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D455" s="10" t="s">
         <v>5</v>
@@ -10170,10 +10119,10 @@
         <v>45961</v>
       </c>
       <c r="B456" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C456" s="9" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D456" s="10" t="s">
         <v>5</v>
@@ -10187,10 +10136,10 @@
         <v>45964</v>
       </c>
       <c r="B457" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C457" s="9" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D457" s="10" t="s">
         <v>5</v>
@@ -10204,10 +10153,10 @@
         <v>45965</v>
       </c>
       <c r="B458" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C458" s="9" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D458" s="10" t="s">
         <v>5</v>
@@ -10221,13 +10170,13 @@
         <v>45965</v>
       </c>
       <c r="B459" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C459" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="D459" s="10" t="s">
-        <v>5</v>
+        <v>496</v>
+      </c>
+      <c r="D459" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E459" s="8" t="s">
         <v>0</v>
@@ -10241,10 +10190,10 @@
         <v>4</v>
       </c>
       <c r="C460" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="D460" s="10" t="s">
-        <v>5</v>
+        <v>497</v>
+      </c>
+      <c r="D460" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E460" s="8" t="s">
         <v>0</v>
@@ -10255,13 +10204,13 @@
         <v>45966</v>
       </c>
       <c r="B461" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C461" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="D461" s="10" t="s">
-        <v>5</v>
+        <v>498</v>
+      </c>
+      <c r="D461" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E461" s="8" t="s">
         <v>0</v>
@@ -10275,16 +10224,16 @@
         <v>4</v>
       </c>
       <c r="C462" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="D462" s="10" t="s">
-        <v>5</v>
+        <v>499</v>
+      </c>
+      <c r="D462" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E462" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="28">
+    <row r="463" spans="1:5">
       <c r="A463" s="7">
         <v>45967</v>
       </c>
@@ -10292,10 +10241,10 @@
         <v>4</v>
       </c>
       <c r="C463" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="D463" s="10" t="s">
-        <v>497</v>
+        <v>500</v>
+      </c>
+      <c r="D463" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E463" s="8" t="s">
         <v>1</v>
@@ -10309,10 +10258,10 @@
         <v>4</v>
       </c>
       <c r="C464" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="D464" s="10" t="s">
-        <v>5</v>
+        <v>501</v>
+      </c>
+      <c r="D464" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E464" s="8" t="s">
         <v>0</v>
@@ -10326,10 +10275,10 @@
         <v>4</v>
       </c>
       <c r="C465" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="D465" s="10" t="s">
-        <v>5</v>
+        <v>502</v>
+      </c>
+      <c r="D465" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E465" s="8" t="s">
         <v>1</v>
@@ -10340,13 +10289,13 @@
         <v>45968</v>
       </c>
       <c r="B466" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C466" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="D466" s="10" t="s">
-        <v>5</v>
+        <v>503</v>
+      </c>
+      <c r="D466" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E466" s="8" t="s">
         <v>1</v>
@@ -10357,10 +10306,10 @@
         <v>45968</v>
       </c>
       <c r="B467" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C467" s="9" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D467" s="10" t="s">
         <v>5</v>
@@ -10374,10 +10323,10 @@
         <v>45971</v>
       </c>
       <c r="B468" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C468" s="9" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D468" s="10" t="s">
         <v>5</v>
@@ -10391,13 +10340,13 @@
         <v>45972</v>
       </c>
       <c r="B469" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C469" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="D469" s="10" t="s">
-        <v>5</v>
+        <v>506</v>
+      </c>
+      <c r="D469" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E469" s="8" t="s">
         <v>0</v>
@@ -10408,13 +10357,13 @@
         <v>45972</v>
       </c>
       <c r="B470" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C470" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="D470" s="10" t="s">
-        <v>5</v>
+        <v>507</v>
+      </c>
+      <c r="D470" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E470" s="8" t="s">
         <v>0</v>
@@ -10425,10 +10374,10 @@
         <v>45972</v>
       </c>
       <c r="B471" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C471" s="9" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D471" s="10" t="s">
         <v>5</v>
@@ -10442,10 +10391,10 @@
         <v>45972</v>
       </c>
       <c r="B472" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C472" s="9" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D472" s="10" t="s">
         <v>5</v>
@@ -10462,10 +10411,10 @@
         <v>4</v>
       </c>
       <c r="C473" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D473" s="10" t="s">
-        <v>5</v>
+        <v>510</v>
+      </c>
+      <c r="D473" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E473" s="8" t="s">
         <v>1</v>
@@ -10479,10 +10428,10 @@
         <v>4</v>
       </c>
       <c r="C474" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="D474" s="10" t="s">
-        <v>5</v>
+        <v>511</v>
+      </c>
+      <c r="D474" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E474" s="8" t="s">
         <v>0</v>
@@ -10496,10 +10445,10 @@
         <v>4</v>
       </c>
       <c r="C475" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="D475" s="10" t="s">
-        <v>5</v>
+        <v>512</v>
+      </c>
+      <c r="D475" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E475" s="8" t="s">
         <v>1</v>
@@ -10510,13 +10459,13 @@
         <v>45975</v>
       </c>
       <c r="B476" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C476" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="D476" s="10" t="s">
-        <v>5</v>
+        <v>513</v>
+      </c>
+      <c r="D476" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E476" s="8" t="s">
         <v>3</v>
@@ -10530,10 +10479,10 @@
         <v>4</v>
       </c>
       <c r="C477" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="D477" s="10" t="s">
-        <v>108</v>
+        <v>514</v>
+      </c>
+      <c r="D477" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E477" s="8" t="s">
         <v>0</v>
@@ -10547,10 +10496,10 @@
         <v>4</v>
       </c>
       <c r="C478" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="D478" s="10" t="s">
-        <v>5</v>
+        <v>515</v>
+      </c>
+      <c r="D478" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E478" s="8" t="s">
         <v>1</v>
@@ -10564,10 +10513,10 @@
         <v>4</v>
       </c>
       <c r="C479" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="D479" s="10" t="s">
-        <v>5</v>
+        <v>516</v>
+      </c>
+      <c r="D479" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E479" s="8" t="s">
         <v>1</v>
@@ -10578,13 +10527,13 @@
         <v>45979</v>
       </c>
       <c r="B480" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C480" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="D480" s="10" t="s">
-        <v>5</v>
+        <v>507</v>
+      </c>
+      <c r="D480" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E480" s="8" t="s">
         <v>1</v>
@@ -10595,13 +10544,13 @@
         <v>45980</v>
       </c>
       <c r="B481" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C481" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="D481" s="10" t="s">
-        <v>5</v>
+        <v>517</v>
+      </c>
+      <c r="D481" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E481" s="8" t="s">
         <v>0</v>
@@ -10612,10 +10561,10 @@
         <v>45981</v>
       </c>
       <c r="B482" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C482" s="9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D482" s="10" t="s">
         <v>5</v>
@@ -10632,10 +10581,10 @@
         <v>4</v>
       </c>
       <c r="C483" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="D483" s="10" t="s">
-        <v>5</v>
+        <v>519</v>
+      </c>
+      <c r="D483" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E483" s="8" t="s">
         <v>0</v>
@@ -10646,13 +10595,13 @@
         <v>45987</v>
       </c>
       <c r="B484" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C484" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="D484" s="10" t="s">
-        <v>5</v>
+        <v>517</v>
+      </c>
+      <c r="D484" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E484" s="8" t="s">
         <v>0</v>
@@ -10663,13 +10612,13 @@
         <v>45987</v>
       </c>
       <c r="B485" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C485" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="D485" s="10" t="s">
-        <v>5</v>
+        <v>520</v>
+      </c>
+      <c r="D485" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E485" s="8" t="s">
         <v>1</v>
@@ -10680,10 +10629,10 @@
         <v>45988</v>
       </c>
       <c r="B486" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C486" s="9" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D486" s="10" t="s">
         <v>5</v>
@@ -10697,13 +10646,13 @@
         <v>45989</v>
       </c>
       <c r="B487" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C487" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="D487" s="10" t="s">
-        <v>5</v>
+        <v>522</v>
+      </c>
+      <c r="D487" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E487" s="8" t="s">
         <v>3</v>
@@ -10714,13 +10663,13 @@
         <v>45989</v>
       </c>
       <c r="B488" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C488" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D488" s="10" t="s">
-        <v>5</v>
+        <v>409</v>
+      </c>
+      <c r="D488" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E488" s="8" t="s">
         <v>1</v>
@@ -10731,10 +10680,10 @@
         <v>45989</v>
       </c>
       <c r="B489" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C489" s="9" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D489" s="10" t="s">
         <v>5</v>
@@ -10748,10 +10697,10 @@
         <v>45992</v>
       </c>
       <c r="B490" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C490" s="9" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D490" s="10" t="s">
         <v>5</v>
@@ -10768,10 +10717,10 @@
         <v>4</v>
       </c>
       <c r="C491" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="D491" s="10" t="s">
-        <v>5</v>
+        <v>525</v>
+      </c>
+      <c r="D491" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E491" s="8" t="s">
         <v>0</v>
@@ -10782,13 +10731,13 @@
         <v>45993</v>
       </c>
       <c r="B492" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C492" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="D492" s="10" t="s">
-        <v>5</v>
+        <v>526</v>
+      </c>
+      <c r="D492" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E492" s="8" t="s">
         <v>3</v>
@@ -10799,10 +10748,10 @@
         <v>45994</v>
       </c>
       <c r="B493" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C493" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D493" s="10" t="s">
         <v>5</v>
@@ -10816,13 +10765,13 @@
         <v>45996</v>
       </c>
       <c r="B494" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C494" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D494" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E494" s="8" t="s">
         <v>3</v>
@@ -10833,13 +10782,13 @@
         <v>45999</v>
       </c>
       <c r="B495" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C495" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="D495" s="10" t="s">
-        <v>5</v>
+        <v>529</v>
+      </c>
+      <c r="D495" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E495" s="8" t="s">
         <v>0</v>
@@ -10853,7 +10802,7 @@
         <v>2</v>
       </c>
       <c r="C496" s="9" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D496" s="10" t="s">
         <v>5</v>
@@ -10867,10 +10816,10 @@
         <v>46000</v>
       </c>
       <c r="B497" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C497" s="9" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D497" s="10" t="s">
         <v>5</v>
@@ -10884,13 +10833,13 @@
         <v>46000</v>
       </c>
       <c r="B498" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C498" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="D498" s="10" t="s">
-        <v>5</v>
+        <v>532</v>
+      </c>
+      <c r="D498" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E498" s="8" t="s">
         <v>0</v>
@@ -10901,10 +10850,10 @@
         <v>46001</v>
       </c>
       <c r="B499" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C499" s="9" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D499" s="10" t="s">
         <v>5</v>
@@ -10918,10 +10867,10 @@
         <v>46003</v>
       </c>
       <c r="B500" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C500" s="9" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D500" s="10" t="s">
         <v>5</v>
@@ -10938,10 +10887,10 @@
         <v>4</v>
       </c>
       <c r="C501" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="D501" s="10" t="s">
-        <v>5</v>
+        <v>535</v>
+      </c>
+      <c r="D501" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E501" s="8" t="s">
         <v>0</v>
@@ -10952,13 +10901,13 @@
         <v>46006</v>
       </c>
       <c r="B502" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C502" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="D502" s="10" t="s">
-        <v>5</v>
+        <v>479</v>
+      </c>
+      <c r="D502" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E502" s="8" t="s">
         <v>3</v>
@@ -10969,13 +10918,13 @@
         <v>46007</v>
       </c>
       <c r="B503" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C503" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="D503" s="10" t="s">
-        <v>5</v>
+        <v>536</v>
+      </c>
+      <c r="D503" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E503" s="8" t="s">
         <v>0</v>
@@ -10986,13 +10935,13 @@
         <v>46007</v>
       </c>
       <c r="B504" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C504" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="D504" s="10" t="s">
-        <v>5</v>
+        <v>537</v>
+      </c>
+      <c r="D504" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E504" s="8" t="s">
         <v>3</v>
@@ -11003,10 +10952,10 @@
         <v>46007</v>
       </c>
       <c r="B505" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C505" s="9" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D505" s="10" t="s">
         <v>5</v>
@@ -11020,13 +10969,13 @@
         <v>46008</v>
       </c>
       <c r="B506" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C506" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="D506" s="10" t="s">
-        <v>5</v>
+        <v>539</v>
+      </c>
+      <c r="D506" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E506" s="8" t="s">
         <v>0</v>
@@ -11037,10 +10986,10 @@
         <v>46008</v>
       </c>
       <c r="B507" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C507" s="9" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D507" s="10" t="s">
         <v>5</v>
@@ -11054,10 +11003,10 @@
         <v>46009</v>
       </c>
       <c r="B508" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C508" s="9" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D508" s="10" t="s">
         <v>5</v>
@@ -11074,10 +11023,10 @@
         <v>4</v>
       </c>
       <c r="C509" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="D509" s="10" t="s">
-        <v>5</v>
+        <v>542</v>
+      </c>
+      <c r="D509" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E509" s="8" t="s">
         <v>0</v>
@@ -11091,10 +11040,10 @@
         <v>4</v>
       </c>
       <c r="C510" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="D510" s="10" t="s">
-        <v>5</v>
+        <v>543</v>
+      </c>
+      <c r="D510" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E510" s="8" t="s">
         <v>1</v>
@@ -11105,10 +11054,10 @@
         <v>46013</v>
       </c>
       <c r="B511" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C511" s="9" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D511" s="10" t="s">
         <v>5</v>
@@ -11122,10 +11071,10 @@
         <v>46013</v>
       </c>
       <c r="B512" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C512" s="9" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D512" s="10" t="s">
         <v>5</v>
@@ -11139,10 +11088,10 @@
         <v>46013</v>
       </c>
       <c r="B513" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C513" s="9" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D513" s="10" t="s">
         <v>5</v>
@@ -11156,13 +11105,13 @@
         <v>46013</v>
       </c>
       <c r="B514" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C514" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="D514" s="10" t="s">
-        <v>5</v>
+        <v>547</v>
+      </c>
+      <c r="D514" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E514" s="8" t="s">
         <v>0</v>
@@ -11173,13 +11122,13 @@
         <v>46014</v>
       </c>
       <c r="B515" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C515" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="D515" s="10" t="s">
-        <v>5</v>
+        <v>548</v>
+      </c>
+      <c r="D515" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E515" s="8" t="s">
         <v>0</v>
@@ -11190,10 +11139,10 @@
         <v>46014</v>
       </c>
       <c r="B516" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C516" s="9" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D516" s="10" t="s">
         <v>5</v>
@@ -11210,10 +11159,10 @@
         <v>4</v>
       </c>
       <c r="C517" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="D517" s="10" t="s">
-        <v>5</v>
+        <v>550</v>
+      </c>
+      <c r="D517" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E517" s="8" t="s">
         <v>0</v>
@@ -11224,13 +11173,13 @@
         <v>46020</v>
       </c>
       <c r="B518" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C518" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="D518" s="10" t="s">
-        <v>5</v>
+        <v>551</v>
+      </c>
+      <c r="D518" s="5" t="s">
+        <v>554</v>
       </c>
       <c r="E518" s="8" t="s">
         <v>0</v>
@@ -11244,10 +11193,10 @@
         <v>4</v>
       </c>
       <c r="C519" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="D519" s="10" t="s">
-        <v>5</v>
+        <v>552</v>
+      </c>
+      <c r="D519" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E519" s="8" t="s">
         <v>0</v>
@@ -11261,10 +11210,10 @@
         <v>4</v>
       </c>
       <c r="C520" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="D520" s="10" t="s">
-        <v>5</v>
+        <v>553</v>
+      </c>
+      <c r="D520" s="17" t="s">
+        <v>422</v>
       </c>
       <c r="E520" s="8" t="s">
         <v>0</v>
@@ -11292,6 +11241,7 @@
       <c r="D1100" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E520" xr:uid="{AF1A4F41-ED03-4033-8789-B5CEC59DDA09}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C54:C79">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>

--- a/교환반품.xlsx
+++ b/교환반품.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\아임반\Desktop\완료된 프로그램\@반품률대시보드\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D1A35B-AB46-400F-B40C-A84D64307DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A59C91-73E8-4367-86B9-A9FC36608C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{54D7FD6B-5922-43C6-B06D-5BC838DADD53}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{54D7FD6B-5922-43C6-B06D-5BC838DADD53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="557">
   <si>
     <t>교환</t>
   </si>
@@ -1429,9 +1429,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>첫구매 당사부담</t>
-  </si>
-  <si>
     <t>202508211959528700</t>
   </si>
   <si>
@@ -1829,6 +1826,18 @@
   </si>
   <si>
     <t>미청구(N배송)</t>
+  </si>
+  <si>
+    <t>첫구매 무료반품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫구매 무료교환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미청구(N배송)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2479,7 +2488,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>75</v>
@@ -2496,7 +2505,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>75</v>
@@ -2513,7 +2522,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>75</v>
@@ -2598,7 +2607,7 @@
         <v>37</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>75</v>
@@ -2632,7 +2641,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>76</v>
@@ -2649,7 +2658,7 @@
         <v>39</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>75</v>
@@ -2700,7 +2709,7 @@
         <v>42</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>75</v>
@@ -2717,7 +2726,7 @@
         <v>43</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>75</v>
@@ -2734,7 +2743,7 @@
         <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>75</v>
@@ -2785,7 +2794,7 @@
         <v>46</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>75</v>
@@ -2802,7 +2811,7 @@
         <v>47</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>75</v>
@@ -2887,7 +2896,7 @@
         <v>52</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>76</v>
@@ -2904,7 +2913,7 @@
         <v>53</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>75</v>
@@ -2921,7 +2930,7 @@
         <v>54</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>75</v>
@@ -2972,7 +2981,7 @@
         <v>56</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>1</v>
@@ -3023,7 +3032,7 @@
         <v>59</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>1</v>
@@ -3040,7 +3049,7 @@
         <v>60</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>1</v>
@@ -3057,7 +3066,7 @@
         <v>61</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>0</v>
@@ -3074,7 +3083,7 @@
         <v>62</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>0</v>
@@ -3091,7 +3100,7 @@
         <v>63</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>0</v>
@@ -3125,7 +3134,7 @@
         <v>65</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>0</v>
@@ -3142,7 +3151,7 @@
         <v>66</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>0</v>
@@ -3176,7 +3185,7 @@
         <v>68</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>1</v>
@@ -3227,7 +3236,7 @@
         <v>71</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>1</v>
@@ -3244,7 +3253,7 @@
         <v>72</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>0</v>
@@ -3261,7 +3270,7 @@
         <v>73</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>0</v>
@@ -3278,7 +3287,7 @@
         <v>74</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>0</v>
@@ -3295,7 +3304,7 @@
         <v>80</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>0</v>
@@ -3363,7 +3372,7 @@
         <v>84</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>1</v>
@@ -3380,7 +3389,7 @@
         <v>85</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>0</v>
@@ -3448,7 +3457,7 @@
         <v>89</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>1</v>
@@ -3516,7 +3525,7 @@
         <v>93</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>1</v>
@@ -3533,7 +3542,7 @@
         <v>94</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>1</v>
@@ -3550,7 +3559,7 @@
         <v>95</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>1</v>
@@ -3567,7 +3576,7 @@
         <v>96</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>0</v>
@@ -3584,7 +3593,7 @@
         <v>97</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>0</v>
@@ -3601,7 +3610,7 @@
         <v>98</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>0</v>
@@ -3652,7 +3661,7 @@
         <v>101</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>1</v>
@@ -3720,7 +3729,7 @@
         <v>105</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>1</v>
@@ -3805,7 +3814,7 @@
         <v>117</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E84" s="14" t="s">
         <v>0</v>
@@ -3839,7 +3848,7 @@
         <v>119</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E86" s="14" t="s">
         <v>0</v>
@@ -3890,7 +3899,7 @@
         <v>122</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E89" s="14" t="s">
         <v>1</v>
@@ -3958,7 +3967,7 @@
         <v>126</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E93" s="14" t="s">
         <v>0</v>
@@ -3975,7 +3984,7 @@
         <v>127</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E94" s="14" t="s">
         <v>0</v>
@@ -4043,7 +4052,7 @@
         <v>131</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>0</v>
@@ -4060,7 +4069,7 @@
         <v>132</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>0</v>
@@ -4077,7 +4086,7 @@
         <v>133</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>0</v>
@@ -4111,7 +4120,7 @@
         <v>135</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E102" s="14" t="s">
         <v>0</v>
@@ -4179,7 +4188,7 @@
         <v>139</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>0</v>
@@ -4196,7 +4205,7 @@
         <v>140</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>0</v>
@@ -4213,7 +4222,7 @@
         <v>141</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>0</v>
@@ -4247,7 +4256,7 @@
         <v>143</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>1</v>
@@ -4281,7 +4290,7 @@
         <v>145</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>0</v>
@@ -4468,7 +4477,7 @@
         <v>156</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E123" s="14" t="s">
         <v>0</v>
@@ -4485,7 +4494,7 @@
         <v>157</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E124" s="14" t="s">
         <v>0</v>
@@ -4553,7 +4562,7 @@
         <v>161</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>1</v>
@@ -4604,7 +4613,7 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>1</v>
@@ -4621,7 +4630,7 @@
         <v>165</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>0</v>
@@ -4651,7 +4660,7 @@
         <v>166</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E134" s="14" t="s">
         <v>0</v>
@@ -4668,7 +4677,7 @@
         <v>167</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E135" s="14" t="s">
         <v>1</v>
@@ -4736,7 +4745,7 @@
         <v>184</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>1</v>
@@ -4753,7 +4762,7 @@
         <v>185</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E140" s="5" t="s">
         <v>1</v>
@@ -4770,7 +4779,7 @@
         <v>186</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E141" s="5" t="s">
         <v>1</v>
@@ -4787,7 +4796,7 @@
         <v>187</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>0</v>
@@ -4804,7 +4813,7 @@
         <v>188</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>1</v>
@@ -4838,7 +4847,7 @@
         <v>190</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E145" s="5" t="s">
         <v>0</v>
@@ -4855,7 +4864,7 @@
         <v>72</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E146" s="5" t="s">
         <v>1</v>
@@ -4889,7 +4898,7 @@
         <v>192</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>1</v>
@@ -4906,7 +4915,7 @@
         <v>193</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E149" s="5" t="s">
         <v>1</v>
@@ -4974,7 +4983,7 @@
         <v>197</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>0</v>
@@ -4991,7 +5000,7 @@
         <v>198</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>0</v>
@@ -5042,7 +5051,7 @@
         <v>201</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E157" s="5" t="s">
         <v>0</v>
@@ -5059,7 +5068,7 @@
         <v>202</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>0</v>
@@ -5076,7 +5085,7 @@
         <v>203</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E159" s="5" t="s">
         <v>0</v>
@@ -5110,7 +5119,7 @@
         <v>205</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>0</v>
@@ -5127,7 +5136,7 @@
         <v>206</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E162" s="5" t="s">
         <v>0</v>
@@ -5144,7 +5153,7 @@
         <v>207</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E163" s="5" t="s">
         <v>0</v>
@@ -5161,7 +5170,7 @@
         <v>208</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E164" s="5" t="s">
         <v>0</v>
@@ -5178,7 +5187,7 @@
         <v>209</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E165" s="5" t="s">
         <v>0</v>
@@ -5195,7 +5204,7 @@
         <v>210</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>1</v>
@@ -5212,7 +5221,7 @@
         <v>211</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E167" s="5" t="s">
         <v>0</v>
@@ -5229,7 +5238,7 @@
         <v>212</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E168" s="5" t="s">
         <v>0</v>
@@ -5280,7 +5289,7 @@
         <v>214</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E171" s="5" t="s">
         <v>1</v>
@@ -5297,7 +5306,7 @@
         <v>214</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E172" s="5" t="s">
         <v>1</v>
@@ -5314,7 +5323,7 @@
         <v>215</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E173" s="5" t="s">
         <v>0</v>
@@ -5331,7 +5340,7 @@
         <v>205</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E174" s="5" t="s">
         <v>0</v>
@@ -5348,7 +5357,7 @@
         <v>216</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E175" s="5" t="s">
         <v>1</v>
@@ -5365,7 +5374,7 @@
         <v>217</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>1</v>
@@ -5382,7 +5391,7 @@
         <v>218</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>1</v>
@@ -5399,7 +5408,7 @@
         <v>219</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E178" s="5" t="s">
         <v>0</v>
@@ -5433,7 +5442,7 @@
         <v>221</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>0</v>
@@ -5450,7 +5459,7 @@
         <v>222</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>0</v>
@@ -5484,7 +5493,7 @@
         <v>224</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E183" s="5" t="s">
         <v>0</v>
@@ -5518,7 +5527,7 @@
         <v>226</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E185" s="5" t="s">
         <v>0</v>
@@ -5552,7 +5561,7 @@
         <v>228</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E187" s="5" t="s">
         <v>0</v>
@@ -5569,7 +5578,7 @@
         <v>229</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E188" s="5" t="s">
         <v>1</v>
@@ -5586,7 +5595,7 @@
         <v>230</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E189" s="5" t="s">
         <v>0</v>
@@ -5620,7 +5629,7 @@
         <v>232</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E191" s="5" t="s">
         <v>0</v>
@@ -5637,7 +5646,7 @@
         <v>233</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E192" s="5" t="s">
         <v>7</v>
@@ -5705,7 +5714,7 @@
         <v>239</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E196" s="5" t="s">
         <v>1</v>
@@ -5722,7 +5731,7 @@
         <v>240</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E197" s="5" t="s">
         <v>1</v>
@@ -5739,7 +5748,7 @@
         <v>241</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E198" s="5" t="s">
         <v>1</v>
@@ -5756,7 +5765,7 @@
         <v>242</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>1</v>
@@ -5790,7 +5799,7 @@
         <v>244</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E201" s="5" t="s">
         <v>0</v>
@@ -5807,7 +5816,7 @@
         <v>245</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E202" s="5" t="s">
         <v>1</v>
@@ -5824,7 +5833,7 @@
         <v>245</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E203" s="5" t="s">
         <v>1</v>
@@ -5841,7 +5850,7 @@
         <v>245</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E204" s="5" t="s">
         <v>1</v>
@@ -5875,7 +5884,7 @@
         <v>247</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E206" s="5" t="s">
         <v>1</v>
@@ -5892,7 +5901,7 @@
         <v>247</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E207" s="5" t="s">
         <v>1</v>
@@ -5909,7 +5918,7 @@
         <v>248</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E208" s="5" t="s">
         <v>0</v>
@@ -5926,7 +5935,7 @@
         <v>249</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E209" s="5" t="s">
         <v>0</v>
@@ -5960,7 +5969,7 @@
         <v>251</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E211" s="5" t="s">
         <v>0</v>
@@ -6028,7 +6037,7 @@
         <v>255</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>0</v>
@@ -6062,7 +6071,7 @@
         <v>257</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>0</v>
@@ -6113,7 +6122,7 @@
         <v>260</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>1</v>
@@ -6130,7 +6139,7 @@
         <v>261</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>0</v>
@@ -6147,7 +6156,7 @@
         <v>262</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E222" s="5" t="s">
         <v>1</v>
@@ -6232,7 +6241,7 @@
         <v>267</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E227" s="5" t="s">
         <v>0</v>
@@ -6283,7 +6292,7 @@
         <v>270</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>0</v>
@@ -6317,7 +6326,7 @@
         <v>251</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E232" s="5" t="s">
         <v>0</v>
@@ -6334,7 +6343,7 @@
         <v>271</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E233" s="5" t="s">
         <v>1</v>
@@ -6351,7 +6360,7 @@
         <v>272</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>1</v>
@@ -6385,7 +6394,7 @@
         <v>274</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E236" s="5" t="s">
         <v>0</v>
@@ -6402,7 +6411,7 @@
         <v>275</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E237" s="5" t="s">
         <v>0</v>
@@ -6419,7 +6428,7 @@
         <v>276</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E238" s="5" t="s">
         <v>0</v>
@@ -6436,7 +6445,7 @@
         <v>277</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>1</v>
@@ -6453,7 +6462,7 @@
         <v>278</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E240" s="5" t="s">
         <v>0</v>
@@ -6487,7 +6496,7 @@
         <v>280</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>1</v>
@@ -6504,7 +6513,7 @@
         <v>281</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>1</v>
@@ -6521,7 +6530,7 @@
         <v>282</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E244" s="5" t="s">
         <v>1</v>
@@ -6538,7 +6547,7 @@
         <v>283</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E245" s="5" t="s">
         <v>1</v>
@@ -6555,7 +6564,7 @@
         <v>284</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E246" s="5" t="s">
         <v>1</v>
@@ -6572,7 +6581,7 @@
         <v>287</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>0</v>
@@ -6606,7 +6615,7 @@
         <v>289</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E249" s="5" t="s">
         <v>1</v>
@@ -6623,7 +6632,7 @@
         <v>290</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E250" s="5" t="s">
         <v>0</v>
@@ -6657,7 +6666,7 @@
         <v>292</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E252" s="5" t="s">
         <v>0</v>
@@ -6674,7 +6683,7 @@
         <v>293</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E253" s="5" t="s">
         <v>0</v>
@@ -6708,7 +6717,7 @@
         <v>295</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E255" s="5" t="s">
         <v>0</v>
@@ -6725,7 +6734,7 @@
         <v>296</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E256" s="5" t="s">
         <v>0</v>
@@ -6793,7 +6802,7 @@
         <v>300</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>0</v>
@@ -6827,7 +6836,7 @@
         <v>302</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>0</v>
@@ -6861,7 +6870,7 @@
         <v>304</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>0</v>
@@ -6895,7 +6904,7 @@
         <v>306</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>0</v>
@@ -6912,7 +6921,7 @@
         <v>290</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E267" s="5" t="s">
         <v>1</v>
@@ -6929,7 +6938,7 @@
         <v>307</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E268" s="5" t="s">
         <v>1</v>
@@ -7031,7 +7040,7 @@
         <v>313</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E274" s="5" t="s">
         <v>0</v>
@@ -7048,7 +7057,7 @@
         <v>314</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>1</v>
@@ -7099,7 +7108,7 @@
         <v>317</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E278" s="5" t="s">
         <v>0</v>
@@ -7150,7 +7159,7 @@
         <v>319</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>0</v>
@@ -7167,7 +7176,7 @@
         <v>320</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>0</v>
@@ -7184,7 +7193,7 @@
         <v>320</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>0</v>
@@ -7252,7 +7261,7 @@
         <v>324</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>0</v>
@@ -7269,7 +7278,7 @@
         <v>325</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E288" s="5" t="s">
         <v>0</v>
@@ -7422,7 +7431,7 @@
         <v>340</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>1</v>
@@ -7439,7 +7448,7 @@
         <v>341</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E298" s="5" t="s">
         <v>0</v>
@@ -7473,7 +7482,7 @@
         <v>343</v>
       </c>
       <c r="D300" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>1</v>
@@ -7490,7 +7499,7 @@
         <v>344</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E301" s="5" t="s">
         <v>1</v>
@@ -7524,7 +7533,7 @@
         <v>346</v>
       </c>
       <c r="D303" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E303" s="5" t="s">
         <v>0</v>
@@ -7541,7 +7550,7 @@
         <v>347</v>
       </c>
       <c r="D304" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E304" s="5" t="s">
         <v>1</v>
@@ -7558,7 +7567,7 @@
         <v>348</v>
       </c>
       <c r="D305" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E305" s="5" t="s">
         <v>1</v>
@@ -7575,7 +7584,7 @@
         <v>349</v>
       </c>
       <c r="D306" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E306" s="5" t="s">
         <v>1</v>
@@ -7592,7 +7601,7 @@
         <v>350</v>
       </c>
       <c r="D307" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E307" s="5" t="s">
         <v>1</v>
@@ -7609,7 +7618,7 @@
         <v>351</v>
       </c>
       <c r="D308" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E308" s="5" t="s">
         <v>1</v>
@@ -7626,7 +7635,7 @@
         <v>352</v>
       </c>
       <c r="D309" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E309" s="5" t="s">
         <v>1</v>
@@ -7643,7 +7652,7 @@
         <v>353</v>
       </c>
       <c r="D310" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E310" s="5" t="s">
         <v>1</v>
@@ -7660,7 +7669,7 @@
         <v>353</v>
       </c>
       <c r="D311" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E311" s="5" t="s">
         <v>1</v>
@@ -7677,7 +7686,7 @@
         <v>354</v>
       </c>
       <c r="D312" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E312" s="5" t="s">
         <v>1</v>
@@ -7694,7 +7703,7 @@
         <v>355</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E313" s="5" t="s">
         <v>0</v>
@@ -7711,7 +7720,7 @@
         <v>356</v>
       </c>
       <c r="D314" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E314" s="5" t="s">
         <v>1</v>
@@ -7745,7 +7754,7 @@
         <v>358</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E316" s="5" t="s">
         <v>1</v>
@@ -7779,7 +7788,7 @@
         <v>360</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E318" s="5" t="s">
         <v>0</v>
@@ -7813,7 +7822,7 @@
         <v>362</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E320" s="5" t="s">
         <v>0</v>
@@ -7847,7 +7856,7 @@
         <v>364</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E322" s="5" t="s">
         <v>0</v>
@@ -7864,7 +7873,7 @@
         <v>365</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E323" s="5" t="s">
         <v>0</v>
@@ -7881,7 +7890,7 @@
         <v>365</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E324" s="5" t="s">
         <v>0</v>
@@ -7898,7 +7907,7 @@
         <v>366</v>
       </c>
       <c r="D325" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>0</v>
@@ -7915,7 +7924,7 @@
         <v>366</v>
       </c>
       <c r="D326" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E326" s="5" t="s">
         <v>0</v>
@@ -7932,7 +7941,7 @@
         <v>367</v>
       </c>
       <c r="D327" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E327" s="5" t="s">
         <v>0</v>
@@ -7983,7 +7992,7 @@
         <v>370</v>
       </c>
       <c r="D330" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E330" s="5" t="s">
         <v>0</v>
@@ -8000,7 +8009,7 @@
         <v>371</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E331" s="5" t="s">
         <v>0</v>
@@ -8017,7 +8026,7 @@
         <v>324</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E332" s="5" t="s">
         <v>1</v>
@@ -8034,7 +8043,7 @@
         <v>372</v>
       </c>
       <c r="D333" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E333" s="5" t="s">
         <v>0</v>
@@ -8051,7 +8060,7 @@
         <v>373</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E334" s="5" t="s">
         <v>0</v>
@@ -8102,7 +8111,7 @@
         <v>376</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E337" s="5" t="s">
         <v>1</v>
@@ -8119,7 +8128,7 @@
         <v>377</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E338" s="5" t="s">
         <v>0</v>
@@ -8136,7 +8145,7 @@
         <v>378</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E339" s="5" t="s">
         <v>0</v>
@@ -8153,7 +8162,7 @@
         <v>379</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E340" s="5" t="s">
         <v>0</v>
@@ -8204,7 +8213,7 @@
         <v>382</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E343" s="5" t="s">
         <v>0</v>
@@ -8272,7 +8281,7 @@
         <v>386</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E347" s="5" t="s">
         <v>6</v>
@@ -8289,7 +8298,7 @@
         <v>387</v>
       </c>
       <c r="D348" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E348" s="5" t="s">
         <v>1</v>
@@ -8323,7 +8332,7 @@
         <v>389</v>
       </c>
       <c r="D350" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E350" s="5" t="s">
         <v>0</v>
@@ -8391,7 +8400,7 @@
         <v>393</v>
       </c>
       <c r="D354" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E354" s="5" t="s">
         <v>1</v>
@@ -8408,7 +8417,7 @@
         <v>394</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E355" s="5" t="s">
         <v>0</v>
@@ -8425,7 +8434,7 @@
         <v>395</v>
       </c>
       <c r="D356" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E356" s="5" t="s">
         <v>1</v>
@@ -8442,7 +8451,7 @@
         <v>396</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E357" s="5" t="s">
         <v>0</v>
@@ -8459,7 +8468,7 @@
         <v>397</v>
       </c>
       <c r="D358" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E358" s="5" t="s">
         <v>0</v>
@@ -8476,7 +8485,7 @@
         <v>398</v>
       </c>
       <c r="D359" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E359" s="5" t="s">
         <v>1</v>
@@ -8510,7 +8519,7 @@
         <v>400</v>
       </c>
       <c r="D361" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E361" s="5" t="s">
         <v>1</v>
@@ -8527,7 +8536,7 @@
         <v>401</v>
       </c>
       <c r="D362" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E362" s="5" t="s">
         <v>0</v>
@@ -8595,7 +8604,7 @@
         <v>405</v>
       </c>
       <c r="D366" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E366" s="5" t="s">
         <v>1</v>
@@ -8612,7 +8621,7 @@
         <v>406</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E367" s="5" t="s">
         <v>0</v>
@@ -8663,7 +8672,7 @@
         <v>409</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E370" s="5" t="s">
         <v>0</v>
@@ -8680,7 +8689,7 @@
         <v>410</v>
       </c>
       <c r="D371" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E371" s="5" t="s">
         <v>0</v>
@@ -8697,7 +8706,7 @@
         <v>411</v>
       </c>
       <c r="D372" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E372" s="5" t="s">
         <v>0</v>
@@ -8714,7 +8723,7 @@
         <v>412</v>
       </c>
       <c r="D373" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E373" s="5" t="s">
         <v>1</v>
@@ -8731,7 +8740,7 @@
         <v>413</v>
       </c>
       <c r="D374" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E374" s="5" t="s">
         <v>1</v>
@@ -8765,7 +8774,7 @@
         <v>415</v>
       </c>
       <c r="D376" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E376" s="5" t="s">
         <v>0</v>
@@ -8799,7 +8808,7 @@
         <v>417</v>
       </c>
       <c r="D378" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E378" s="5" t="s">
         <v>0</v>
@@ -8816,7 +8825,7 @@
         <v>418</v>
       </c>
       <c r="D379" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E379" s="5" t="s">
         <v>0</v>
@@ -8850,7 +8859,7 @@
         <v>420</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E381" s="5" t="s">
         <v>0</v>
@@ -8864,7 +8873,7 @@
         <v>182</v>
       </c>
       <c r="C382" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D382" s="10" t="s">
         <v>5</v>
@@ -8881,7 +8890,7 @@
         <v>337</v>
       </c>
       <c r="C383" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D383" s="10" t="s">
         <v>5</v>
@@ -8898,10 +8907,10 @@
         <v>21</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E384" s="8" t="s">
         <v>0</v>
@@ -8915,10 +8924,10 @@
         <v>21</v>
       </c>
       <c r="C385" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E385" s="8" t="s">
         <v>0</v>
@@ -8935,7 +8944,7 @@
         <v>360</v>
       </c>
       <c r="D386" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E386" s="8" t="s">
         <v>0</v>
@@ -8949,10 +8958,10 @@
         <v>21</v>
       </c>
       <c r="C387" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E387" s="8" t="s">
         <v>1</v>
@@ -8966,10 +8975,10 @@
         <v>21</v>
       </c>
       <c r="C388" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E388" s="8" t="s">
         <v>0</v>
@@ -8983,10 +8992,10 @@
         <v>4</v>
       </c>
       <c r="C389" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D389" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E389" s="8" t="s">
         <v>0</v>
@@ -9000,7 +9009,7 @@
         <v>337</v>
       </c>
       <c r="C390" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D390" s="10" t="s">
         <v>5</v>
@@ -9017,10 +9026,10 @@
         <v>4</v>
       </c>
       <c r="C391" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D391" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E391" s="8" t="s">
         <v>0</v>
@@ -9034,10 +9043,10 @@
         <v>21</v>
       </c>
       <c r="C392" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D392" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E392" s="8" t="s">
         <v>0</v>
@@ -9051,7 +9060,7 @@
         <v>2</v>
       </c>
       <c r="C393" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D393" s="10" t="s">
         <v>5</v>
@@ -9068,10 +9077,10 @@
         <v>4</v>
       </c>
       <c r="C394" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D394" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E394" s="8" t="s">
         <v>1</v>
@@ -9085,10 +9094,10 @@
         <v>21</v>
       </c>
       <c r="C395" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E395" s="8" t="s">
         <v>1</v>
@@ -9102,7 +9111,7 @@
         <v>77</v>
       </c>
       <c r="C396" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D396" s="10" t="s">
         <v>5</v>
@@ -9119,10 +9128,10 @@
         <v>79</v>
       </c>
       <c r="C397" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D397" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E397" s="8" t="s">
         <v>0</v>
@@ -9139,7 +9148,7 @@
         <v>360</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E398" s="8" t="s">
         <v>1</v>
@@ -9153,10 +9162,10 @@
         <v>4</v>
       </c>
       <c r="C399" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D399" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E399" s="8" t="s">
         <v>1</v>
@@ -9170,10 +9179,10 @@
         <v>4</v>
       </c>
       <c r="C400" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D400" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E400" s="8" t="s">
         <v>1</v>
@@ -9187,10 +9196,10 @@
         <v>21</v>
       </c>
       <c r="C401" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E401" s="8" t="s">
         <v>0</v>
@@ -9204,10 +9213,10 @@
         <v>4</v>
       </c>
       <c r="C402" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D402" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E402" s="8" t="s">
         <v>1</v>
@@ -9221,7 +9230,7 @@
         <v>179</v>
       </c>
       <c r="C403" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D403" s="10" t="s">
         <v>5</v>
@@ -9238,7 +9247,7 @@
         <v>182</v>
       </c>
       <c r="C404" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D404" s="10" t="s">
         <v>5</v>
@@ -9255,10 +9264,10 @@
         <v>4</v>
       </c>
       <c r="C405" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D405" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E405" s="8" t="s">
         <v>1</v>
@@ -9272,10 +9281,10 @@
         <v>4</v>
       </c>
       <c r="C406" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D406" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E406" s="8" t="s">
         <v>1</v>
@@ -9292,7 +9301,7 @@
         <v>254</v>
       </c>
       <c r="D407" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E407" s="8" t="s">
         <v>1</v>
@@ -9306,10 +9315,10 @@
         <v>4</v>
       </c>
       <c r="C408" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D408" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E408" s="8" t="s">
         <v>0</v>
@@ -9323,10 +9332,10 @@
         <v>4</v>
       </c>
       <c r="C409" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D409" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E409" s="8" t="s">
         <v>0</v>
@@ -9340,10 +9349,10 @@
         <v>21</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E410" s="8" t="s">
         <v>0</v>
@@ -9357,10 +9366,10 @@
         <v>21</v>
       </c>
       <c r="C411" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E411" s="8" t="s">
         <v>0</v>
@@ -9374,10 +9383,10 @@
         <v>21</v>
       </c>
       <c r="C412" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E412" s="8" t="s">
         <v>0</v>
@@ -9391,7 +9400,7 @@
         <v>182</v>
       </c>
       <c r="C413" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D413" s="10" t="s">
         <v>5</v>
@@ -9408,10 +9417,10 @@
         <v>21</v>
       </c>
       <c r="C414" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E414" s="8" t="s">
         <v>0</v>
@@ -9425,10 +9434,10 @@
         <v>21</v>
       </c>
       <c r="C415" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E415" s="8" t="s">
         <v>1</v>
@@ -9442,7 +9451,7 @@
         <v>182</v>
       </c>
       <c r="C416" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D416" s="10" t="s">
         <v>5</v>
@@ -9459,7 +9468,7 @@
         <v>79</v>
       </c>
       <c r="C417" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D417" s="10" t="s">
         <v>5</v>
@@ -9476,10 +9485,10 @@
         <v>21</v>
       </c>
       <c r="C418" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E418" s="8" t="s">
         <v>0</v>
@@ -9493,10 +9502,10 @@
         <v>4</v>
       </c>
       <c r="C419" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D419" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E419" s="8" t="s">
         <v>0</v>
@@ -9510,10 +9519,10 @@
         <v>4</v>
       </c>
       <c r="C420" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D420" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E420" s="8" t="s">
         <v>1</v>
@@ -9527,7 +9536,7 @@
         <v>337</v>
       </c>
       <c r="C421" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D421" s="10" t="s">
         <v>5</v>
@@ -9544,10 +9553,10 @@
         <v>4</v>
       </c>
       <c r="C422" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D422" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E422" s="8" t="s">
         <v>1</v>
@@ -9561,10 +9570,10 @@
         <v>4</v>
       </c>
       <c r="C423" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D423" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E423" s="8" t="s">
         <v>1</v>
@@ -9578,10 +9587,10 @@
         <v>4</v>
       </c>
       <c r="C424" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D424" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E424" s="8" t="s">
         <v>1</v>
@@ -9595,10 +9604,10 @@
         <v>4</v>
       </c>
       <c r="C425" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D425" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E425" s="8" t="s">
         <v>1</v>
@@ -9612,10 +9621,10 @@
         <v>4</v>
       </c>
       <c r="C426" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D426" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E426" s="8" t="s">
         <v>1</v>
@@ -9629,7 +9638,7 @@
         <v>77</v>
       </c>
       <c r="C427" s="9" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D427" s="10" t="s">
         <v>5</v>
@@ -9646,7 +9655,7 @@
         <v>77</v>
       </c>
       <c r="C428" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D428" s="10" t="s">
         <v>5</v>
@@ -9663,10 +9672,10 @@
         <v>21</v>
       </c>
       <c r="C429" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E429" s="8" t="s">
         <v>0</v>
@@ -9680,7 +9689,7 @@
         <v>182</v>
       </c>
       <c r="C430" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D430" s="10" t="s">
         <v>5</v>
@@ -9697,10 +9706,10 @@
         <v>4</v>
       </c>
       <c r="C431" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D431" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E431" s="8" t="s">
         <v>0</v>
@@ -9714,10 +9723,10 @@
         <v>21</v>
       </c>
       <c r="C432" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E432" s="8" t="s">
         <v>0</v>
@@ -9731,7 +9740,7 @@
         <v>79</v>
       </c>
       <c r="C433" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D433" s="10" t="s">
         <v>5</v>
@@ -9748,7 +9757,7 @@
         <v>79</v>
       </c>
       <c r="C434" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D434" s="10" t="s">
         <v>5</v>
@@ -9765,7 +9774,7 @@
         <v>77</v>
       </c>
       <c r="C435" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D435" s="10" t="s">
         <v>5</v>
@@ -9782,7 +9791,7 @@
         <v>2</v>
       </c>
       <c r="C436" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D436" s="10" t="s">
         <v>5</v>
@@ -9799,7 +9808,7 @@
         <v>111</v>
       </c>
       <c r="C437" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D437" s="10" t="s">
         <v>5</v>
@@ -9816,10 +9825,10 @@
         <v>21</v>
       </c>
       <c r="C438" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D438" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E438" s="8" t="s">
         <v>0</v>
@@ -9833,10 +9842,10 @@
         <v>4</v>
       </c>
       <c r="C439" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D439" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E439" s="8" t="s">
         <v>0</v>
@@ -9850,7 +9859,7 @@
         <v>112</v>
       </c>
       <c r="C440" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D440" s="10" t="s">
         <v>5</v>
@@ -9867,7 +9876,7 @@
         <v>111</v>
       </c>
       <c r="C441" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D441" s="10" t="s">
         <v>5</v>
@@ -9884,10 +9893,10 @@
         <v>21</v>
       </c>
       <c r="C442" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D442" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E442" s="8" t="s">
         <v>0</v>
@@ -9901,10 +9910,10 @@
         <v>4</v>
       </c>
       <c r="C443" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D443" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E443" s="8" t="s">
         <v>0</v>
@@ -9918,10 +9927,10 @@
         <v>21</v>
       </c>
       <c r="C444" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E444" s="8" t="s">
         <v>7</v>
@@ -9935,7 +9944,7 @@
         <v>111</v>
       </c>
       <c r="C445" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D445" s="10" t="s">
         <v>5</v>
@@ -9952,7 +9961,7 @@
         <v>111</v>
       </c>
       <c r="C446" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D446" s="10" t="s">
         <v>5</v>
@@ -9969,7 +9978,7 @@
         <v>111</v>
       </c>
       <c r="C447" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D447" s="10" t="s">
         <v>5</v>
@@ -9986,10 +9995,10 @@
         <v>21</v>
       </c>
       <c r="C448" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D448" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E448" s="8" t="s">
         <v>0</v>
@@ -10003,7 +10012,7 @@
         <v>79</v>
       </c>
       <c r="C449" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D449" s="10" t="s">
         <v>5</v>
@@ -10020,10 +10029,10 @@
         <v>21</v>
       </c>
       <c r="C450" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D450" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E450" s="8" t="s">
         <v>0</v>
@@ -10037,10 +10046,10 @@
         <v>21</v>
       </c>
       <c r="C451" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E451" s="8" t="s">
         <v>3</v>
@@ -10054,10 +10063,10 @@
         <v>4</v>
       </c>
       <c r="C452" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D452" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E452" s="8" t="s">
         <v>0</v>
@@ -10071,10 +10080,10 @@
         <v>4</v>
       </c>
       <c r="C453" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D453" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E453" s="8" t="s">
         <v>0</v>
@@ -10088,10 +10097,10 @@
         <v>4</v>
       </c>
       <c r="C454" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D454" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E454" s="8" t="s">
         <v>1</v>
@@ -10105,7 +10114,7 @@
         <v>111</v>
       </c>
       <c r="C455" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D455" s="10" t="s">
         <v>5</v>
@@ -10122,7 +10131,7 @@
         <v>77</v>
       </c>
       <c r="C456" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D456" s="10" t="s">
         <v>5</v>
@@ -10139,7 +10148,7 @@
         <v>79</v>
       </c>
       <c r="C457" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D457" s="10" t="s">
         <v>5</v>
@@ -10156,7 +10165,7 @@
         <v>77</v>
       </c>
       <c r="C458" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D458" s="10" t="s">
         <v>5</v>
@@ -10173,10 +10182,10 @@
         <v>21</v>
       </c>
       <c r="C459" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D459" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E459" s="8" t="s">
         <v>0</v>
@@ -10190,10 +10199,10 @@
         <v>4</v>
       </c>
       <c r="C460" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D460" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E460" s="8" t="s">
         <v>0</v>
@@ -10207,10 +10216,10 @@
         <v>21</v>
       </c>
       <c r="C461" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D461" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E461" s="8" t="s">
         <v>0</v>
@@ -10224,10 +10233,10 @@
         <v>4</v>
       </c>
       <c r="C462" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D462" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E462" s="8" t="s">
         <v>1</v>
@@ -10241,10 +10250,10 @@
         <v>4</v>
       </c>
       <c r="C463" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D463" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E463" s="8" t="s">
         <v>1</v>
@@ -10258,10 +10267,10 @@
         <v>4</v>
       </c>
       <c r="C464" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D464" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E464" s="8" t="s">
         <v>0</v>
@@ -10275,10 +10284,10 @@
         <v>4</v>
       </c>
       <c r="C465" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D465" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E465" s="8" t="s">
         <v>1</v>
@@ -10292,10 +10301,10 @@
         <v>21</v>
       </c>
       <c r="C466" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D466" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E466" s="8" t="s">
         <v>1</v>
@@ -10309,7 +10318,7 @@
         <v>24</v>
       </c>
       <c r="C467" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D467" s="10" t="s">
         <v>5</v>
@@ -10326,7 +10335,7 @@
         <v>79</v>
       </c>
       <c r="C468" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D468" s="10" t="s">
         <v>5</v>
@@ -10343,10 +10352,10 @@
         <v>21</v>
       </c>
       <c r="C469" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E469" s="8" t="s">
         <v>0</v>
@@ -10360,10 +10369,10 @@
         <v>21</v>
       </c>
       <c r="C470" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E470" s="8" t="s">
         <v>0</v>
@@ -10377,7 +10386,7 @@
         <v>77</v>
       </c>
       <c r="C471" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D471" s="10" t="s">
         <v>5</v>
@@ -10394,7 +10403,7 @@
         <v>77</v>
       </c>
       <c r="C472" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D472" s="10" t="s">
         <v>5</v>
@@ -10411,10 +10420,10 @@
         <v>4</v>
       </c>
       <c r="C473" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D473" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E473" s="8" t="s">
         <v>1</v>
@@ -10428,10 +10437,10 @@
         <v>4</v>
       </c>
       <c r="C474" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D474" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E474" s="8" t="s">
         <v>0</v>
@@ -10445,10 +10454,10 @@
         <v>4</v>
       </c>
       <c r="C475" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D475" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E475" s="8" t="s">
         <v>1</v>
@@ -10462,10 +10471,10 @@
         <v>21</v>
       </c>
       <c r="C476" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E476" s="8" t="s">
         <v>3</v>
@@ -10479,10 +10488,10 @@
         <v>4</v>
       </c>
       <c r="C477" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D477" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E477" s="8" t="s">
         <v>0</v>
@@ -10496,10 +10505,10 @@
         <v>4</v>
       </c>
       <c r="C478" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D478" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E478" s="8" t="s">
         <v>1</v>
@@ -10513,10 +10522,10 @@
         <v>4</v>
       </c>
       <c r="C479" s="9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D479" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E479" s="8" t="s">
         <v>1</v>
@@ -10530,10 +10539,10 @@
         <v>21</v>
       </c>
       <c r="C480" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D480" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E480" s="8" t="s">
         <v>1</v>
@@ -10547,10 +10556,10 @@
         <v>21</v>
       </c>
       <c r="C481" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D481" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E481" s="8" t="s">
         <v>0</v>
@@ -10564,7 +10573,7 @@
         <v>79</v>
       </c>
       <c r="C482" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D482" s="10" t="s">
         <v>5</v>
@@ -10581,10 +10590,10 @@
         <v>4</v>
       </c>
       <c r="C483" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D483" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E483" s="8" t="s">
         <v>0</v>
@@ -10598,10 +10607,10 @@
         <v>21</v>
       </c>
       <c r="C484" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E484" s="8" t="s">
         <v>0</v>
@@ -10615,10 +10624,10 @@
         <v>21</v>
       </c>
       <c r="C485" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E485" s="8" t="s">
         <v>1</v>
@@ -10632,7 +10641,7 @@
         <v>337</v>
       </c>
       <c r="C486" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D486" s="10" t="s">
         <v>5</v>
@@ -10649,10 +10658,10 @@
         <v>21</v>
       </c>
       <c r="C487" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D487" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E487" s="8" t="s">
         <v>3</v>
@@ -10669,7 +10678,7 @@
         <v>409</v>
       </c>
       <c r="D488" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E488" s="8" t="s">
         <v>1</v>
@@ -10683,7 +10692,7 @@
         <v>337</v>
       </c>
       <c r="C489" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D489" s="10" t="s">
         <v>5</v>
@@ -10700,7 +10709,7 @@
         <v>77</v>
       </c>
       <c r="C490" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D490" s="10" t="s">
         <v>5</v>
@@ -10717,10 +10726,10 @@
         <v>4</v>
       </c>
       <c r="C491" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D491" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E491" s="8" t="s">
         <v>0</v>
@@ -10734,10 +10743,10 @@
         <v>21</v>
       </c>
       <c r="C492" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D492" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E492" s="8" t="s">
         <v>3</v>
@@ -10751,7 +10760,7 @@
         <v>182</v>
       </c>
       <c r="C493" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D493" s="10" t="s">
         <v>5</v>
@@ -10768,7 +10777,7 @@
         <v>79</v>
       </c>
       <c r="C494" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D494" s="10" t="s">
         <v>108</v>
@@ -10785,10 +10794,10 @@
         <v>21</v>
       </c>
       <c r="C495" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E495" s="8" t="s">
         <v>0</v>
@@ -10802,7 +10811,7 @@
         <v>2</v>
       </c>
       <c r="C496" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D496" s="10" t="s">
         <v>5</v>
@@ -10819,7 +10828,7 @@
         <v>79</v>
       </c>
       <c r="C497" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D497" s="10" t="s">
         <v>5</v>
@@ -10836,10 +10845,10 @@
         <v>21</v>
       </c>
       <c r="C498" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E498" s="8" t="s">
         <v>0</v>
@@ -10853,7 +10862,7 @@
         <v>77</v>
       </c>
       <c r="C499" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D499" s="10" t="s">
         <v>5</v>
@@ -10870,7 +10879,7 @@
         <v>79</v>
       </c>
       <c r="C500" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D500" s="10" t="s">
         <v>5</v>
@@ -10887,10 +10896,10 @@
         <v>4</v>
       </c>
       <c r="C501" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D501" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E501" s="8" t="s">
         <v>0</v>
@@ -10904,10 +10913,10 @@
         <v>21</v>
       </c>
       <c r="C502" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D502" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E502" s="8" t="s">
         <v>3</v>
@@ -10921,10 +10930,10 @@
         <v>21</v>
       </c>
       <c r="C503" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D503" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E503" s="8" t="s">
         <v>0</v>
@@ -10938,10 +10947,10 @@
         <v>21</v>
       </c>
       <c r="C504" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D504" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E504" s="8" t="s">
         <v>3</v>
@@ -10955,7 +10964,7 @@
         <v>182</v>
       </c>
       <c r="C505" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D505" s="10" t="s">
         <v>5</v>
@@ -10972,10 +10981,10 @@
         <v>21</v>
       </c>
       <c r="C506" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D506" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E506" s="8" t="s">
         <v>0</v>
@@ -10989,7 +10998,7 @@
         <v>77</v>
       </c>
       <c r="C507" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D507" s="10" t="s">
         <v>5</v>
@@ -11006,7 +11015,7 @@
         <v>182</v>
       </c>
       <c r="C508" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D508" s="10" t="s">
         <v>5</v>
@@ -11023,10 +11032,10 @@
         <v>4</v>
       </c>
       <c r="C509" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D509" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E509" s="8" t="s">
         <v>0</v>
@@ -11040,10 +11049,10 @@
         <v>4</v>
       </c>
       <c r="C510" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D510" s="17" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="E510" s="8" t="s">
         <v>1</v>
@@ -11057,7 +11066,7 @@
         <v>77</v>
       </c>
       <c r="C511" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D511" s="10" t="s">
         <v>5</v>
@@ -11074,7 +11083,7 @@
         <v>77</v>
       </c>
       <c r="C512" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D512" s="10" t="s">
         <v>5</v>
@@ -11091,7 +11100,7 @@
         <v>79</v>
       </c>
       <c r="C513" s="9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D513" s="10" t="s">
         <v>5</v>
@@ -11108,10 +11117,10 @@
         <v>21</v>
       </c>
       <c r="C514" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D514" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E514" s="8" t="s">
         <v>0</v>
@@ -11125,10 +11134,10 @@
         <v>21</v>
       </c>
       <c r="C515" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D515" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E515" s="8" t="s">
         <v>0</v>
@@ -11142,7 +11151,7 @@
         <v>109</v>
       </c>
       <c r="C516" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D516" s="10" t="s">
         <v>5</v>
@@ -11159,10 +11168,10 @@
         <v>4</v>
       </c>
       <c r="C517" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D517" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E517" s="8" t="s">
         <v>0</v>
@@ -11176,10 +11185,10 @@
         <v>21</v>
       </c>
       <c r="C518" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D518" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E518" s="8" t="s">
         <v>0</v>
@@ -11193,10 +11202,10 @@
         <v>4</v>
       </c>
       <c r="C519" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D519" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E519" s="8" t="s">
         <v>0</v>
@@ -11210,10 +11219,10 @@
         <v>4</v>
       </c>
       <c r="C520" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D520" s="17" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="E520" s="8" t="s">
         <v>0</v>
